--- a/セリフ編集/キャラタイプ別/標準×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×寡黙.xlsx
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分け。……いつか、続きを。</t>
+          <t xml:space="preserve">……決着つかず。いつか、続きを。</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/キャラタイプ別/標準×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×寡黙.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -342,22 +342,22 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.standard.hit[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.standard.hit[1]</t>
+          <t xml:space="preserve">atk.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -367,29 +367,29 @@
       </c>
       <c r="F2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あなたたち相手に、ここでは終われない。</t>
+          <t xml:space="preserve">…まだ、終わらない</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.standard.hit[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.standard.hit[2]</t>
+          <t xml:space="preserve">atk.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -399,29 +399,29 @@
       </c>
       <c r="F3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、立てる。</t>
+          <t xml:space="preserve">…ここからよ</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.standard.win[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.standard.win[1]</t>
+          <t xml:space="preserve">atk.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -431,29 +431,29 @@
       </c>
       <c r="F4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これが、答え。切られて、終わりじゃなかった。</t>
+          <t xml:space="preserve">…負けるわけにはいかない</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.standard.win[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.quiet[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.standard.win[2]</t>
+          <t xml:space="preserve">atk.standard.quiet[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -463,1100 +463,3980 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あそこを出て、私はまだ戦えてる。それだけ。</t>
+          <t xml:space="preserve">…見ていて</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.lose[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.lose[1]</t>
+          <t xml:space="preserve">bigmove.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けです。ごめんなさい。</t>
+          <t xml:space="preserve">……いく</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.lose[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.lose[2]</t>
+          <t xml:space="preserve">bigmove.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。……悔しい、とだけ。</t>
+          <t xml:space="preserve">……これで</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.lose[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.lose[3]</t>
+          <t xml:space="preserve">bigmove.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、違います。</t>
+          <t xml:space="preserve">……終わりだ</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.petition[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.petition[1]</t>
+          <t xml:space="preserve">climax.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。あの人と、やらせてください。</t>
+          <t xml:space="preserve">（…集中。今だけは、何も考えなくていい）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.petition[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.petition[2]</t>
+          <t xml:space="preserve">climax.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……お願いがあります。あの人です。</t>
+          <t xml:space="preserve">（…身体が軽い。いける）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.petition[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.petition[3]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一つだけ。あの人と、組んでください。</t>
+          <t xml:space="preserve">……まだ</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.sendoff[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.sendoff[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとうございます。行ってきます。</t>
+          <t xml:space="preserve">……これくらい</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.sendoff[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.sendoff[2]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はい。……無駄にはしません。</t>
+          <t xml:space="preserve">……立てる</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.sendoff[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.quiet.hit[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.sendoff[3]</t>
+          <t xml:space="preserve">standard.quiet.hit[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、迷いはないです。</t>
+          <t xml:space="preserve">……あなたたち相手に、ここでは終われない。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.quiet.hit[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.win[1]</t>
+          <t xml:space="preserve">standard.quiet.hit[2]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝ちました。</t>
+          <t xml:space="preserve">……まだ、立てる。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.quiet.win[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.win[2]</t>
+          <t xml:space="preserve">standard.quiet.win[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちです。……以上です。</t>
+          <t xml:space="preserve">……これが、答え。切られて、終わりじゃなかった。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.win[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.quiet.win[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.win[3]</t>
+          <t xml:space="preserve">standard.quiet.win[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。……それだけ、伝えたくて。</t>
+          <t xml:space="preserve">……あそこを出て、私はまだ戦えてる。それだけ。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet._accept[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet._accept[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……受ける。それだけ。</t>
+          <t xml:space="preserve">……動けない</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet._accept[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet._accept[2]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わかった。言葉はいらない。</t>
+          <t xml:space="preserve">……間に合わない</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet._accept[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet._accept[3]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……逃げない。来て。</t>
+          <t xml:space="preserve">…させない</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.draw[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.draw[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……つかなかった。決着は。</t>
+          <t xml:space="preserve">…まだ</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.draw[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.draw[2]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決着つかず。いつか、続きを。</t>
+          <t xml:space="preserve">…駄目</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.draw[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.draw[3]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、終わってない。</t>
+          <t xml:space="preserve">…合わせる</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.lose[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.lose[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。何も言えない。</t>
+          <t xml:space="preserve">…せーの</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.lose[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.lose[2]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたの勝ち。……失礼する。</t>
+          <t xml:space="preserve">…いこう</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.lose[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.lose[3]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悔しい。それだけ。</t>
+          <t xml:space="preserve">…交代</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.win[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.win[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。以上。</t>
+          <t xml:space="preserve">…来た、私が</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.win[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.win[2]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わり。……強かった、あなた。</t>
+          <t xml:space="preserve">…任せて</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.win[3]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_quiet.win[3]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ち。それだけ伝えておく。</t>
+          <t xml:space="preserve">…{partner}、ごめん。</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES.quiet.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.standard[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あっち側とは、違う。それだけ。</t>
+          <t xml:space="preserve">…悔しい。{partner}にも、申し訳ない。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.quiet.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.standard[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……え。……そんな……。</t>
+          <t xml:space="preserve">…{partner}、ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.quiet.standard[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.standard[2]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いやだ。</t>
+          <t xml:space="preserve">…{partner}と、だから勝てた。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.quiet.standard[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.lose[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.standard[1]</t>
+          <t xml:space="preserve">standard_quiet.lose[1]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめん。もう、ここにはいられない。</t>
+          <t xml:space="preserve">……負けです。ごめんなさい。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.quiet.standard[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.lose[2]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.standard[2]</t>
+          <t xml:space="preserve">standard_quiet.lose[2]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あたし、あっち側に……行きたい。</t>
+          <t xml:space="preserve">負けました。……悔しい、とだけ。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.quiet.standard[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.lose[3]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.standard[1]</t>
+          <t xml:space="preserve">standard_quiet.lose[3]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この扱い、納得してない。</t>
+          <t xml:space="preserve">……次は、違います。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.quiet.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.petition[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.standard.high[1]</t>
+          <t xml:space="preserve">standard_quiet.petition[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">社長。あの人と、やらせてください。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.quiet.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.petition[2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.standard.high[1]</t>
+          <t xml:space="preserve">standard_quiet.petition[2]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">……お願いがあります。あの人です。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.quiet.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.petition[3]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.standard.high[1]</t>
+          <t xml:space="preserve">standard_quiet.petition[3]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今夜で、終わらせる</t>
+          <t xml:space="preserve">一つだけ。あの人と、組んでください。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.quiet.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.sendoff[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.sendoff[1]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ありがとうございます。行ってきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.sendoff[2]</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.sendoff[2]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">はい。……無駄にはしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.sendoff[3]</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.sendoff[3]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……もう、迷いはないです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.win[1]</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.win[1]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝ちました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.win[2]</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.win[2]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちです。……以上です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_quiet.win[3]</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.win[3]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました。……それだけ、伝えたくて。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet._accept[1]</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet._accept[1]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……受ける。それだけ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet._accept[2]</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet._accept[2]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わかった。言葉はいらない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet._accept[3]</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet._accept[3]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……逃げない。来て。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.draw[1]</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.draw[1]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……つかなかった。決着は。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.draw[2]</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.draw[2]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……決着つかず。いつか、続きを。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.draw[3]</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.draw[3]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……まだ、終わってない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.lose[1]</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.lose[1]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……負けた。何も言えない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.lose[2]</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.lose[2]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あなたの勝ち。……失礼する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.lose[3]</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.lose[3]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……悔しい。それだけ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.win[1]</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.win[1]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。以上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.win[2]</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.win[2]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">終わり。……強かった、あなた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_quiet.win[3]</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_quiet.win[3]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ち。それだけ伝えておく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長、私たちのメンバーを、ちゃんと見てもらえるとありがたいです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長、次のメイン、私たちで挑ませてもらえませんか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長、待遇のことで相談があります。私たちのメンバーのことです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長、私たちの仕事、見てもらえてますか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…見てもらえてるんだ、って、安心しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、すみません。出過ぎたことを言いました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…そっちでしたか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。やります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、わかりました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですね。ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。みんな、喜びます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、わかりました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくださって、嬉しいです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…見てもらえてたんですね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、わかりました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…そっちで返してくださるんですね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、すみません。…悪気は、なかったんですけど。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…でも、少し、考えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、すみません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="40" customHeight="1">
+      <c r="A77" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、わかりました。…やりすぎ、でしたね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…ヒールの仕事、続けます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="40" customHeight="1">
+      <c r="A79" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…申し訳ありません。…出ます、ちゃんと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…気を遣っていただいて。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="40" customHeight="1">
+      <c r="A81" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…私の代わりに、みんなを見てくださって。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="40" customHeight="1">
+      <c r="A82" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…少し、休みます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、平気です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="40" customHeight="1">
+      <c r="A84" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…メンバーが受け止めてくれると、助かります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="40" customHeight="1">
+      <c r="A85" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、…わかりました。気をつけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="40" customHeight="1">
+      <c r="A86" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="40" customHeight="1">
+      <c r="A87" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…下の子のフォロー、助かります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="40" customHeight="1">
+      <c r="A88" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、すみません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="40" customHeight="1">
+      <c r="A89" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">（…何も言わず、目を伏せた）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="40" customHeight="1">
+      <c r="A90" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="40" customHeight="1">
+      <c r="A91" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はい、…わかりました。やりすぎ、だったかもしれません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="40" customHeight="1">
+      <c r="A92" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…見守ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="40" customHeight="1">
+      <c r="A93" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。…下の子、限界が近かったかもしれません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="40" customHeight="1">
+      <c r="A94" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.attack.standard</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.attack.standard</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……もう、戻れません</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="40" customHeight="1">
+      <c r="A95" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.defend.standard</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.defend.standard</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">そちらが望むなら</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="40" customHeight="1">
+      <c r="A96" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr" s="2">
+      <c r="C96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……もう、ついていけない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="40" customHeight="1">
+      <c r="A97" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……息が、できない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……意外と、普通に、話せるね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……もう、逃げない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.quiet.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……負けた、けど……組は、潰れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.quiet.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次は、ない、なんて……思ってない</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.quiet.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">（沈黙）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.quiet.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……っ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.quiet.high[2]</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[2]</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……これで、終わり。じゃない</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.quiet.low[1]</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.low[1]</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（深く息をつく）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.quiet.mid[1]</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.mid[1]</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝てた</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……話すことは、もうない</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.high[2]</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[2]</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……行こう。リングが、待ってる</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.high[3]</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[3]</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……うちらの組のこと、悪く言う声は、ぜんぶ今日で消す</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.low[1]</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.low[1]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……うん。受けて立つ</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.mid[1]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.mid[1]</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……来なよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……分かった。リングで</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.quiet.high[2]</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[2]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……うん。逃げない</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.quiet.low[1]</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.low[1]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……分かった</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.quiet.mid[1]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.mid[1]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……いいよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES.standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……負けた。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES.standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……すまない</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES.standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……行く</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……今夜で、終わらせる</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">quiet.standard.high[1]</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr" s="3">
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……いいよ。来な</t>
         </is>
       </c>
     </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.quiet.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……負けた</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.quiet.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……うむ</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES.standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……時間だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.quiet.high[2]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[2]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……席を、もらいに来た</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……いいだろう</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H39"/>
+  <autoFilter ref="A1:H129"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×寡黙.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H415"/>
+  <dimension ref="A1:H417"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいだろう</t>
+          <t xml:space="preserve">……いいわ</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい……。{tenure}私なんかいなくても……変わらないと思うんです……。</t>
+          <t xml:space="preserve">……ごめんなさい……。{tenure}私がいなくても……変わらないと思うんです……。</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うちらの組のこと、悪く言う声は、ぜんぶ今日で消す</t>
+          <t xml:space="preserve">……うちの組のこと、悪く言う声は、ぜんぶ今日で消す</t>
         </is>
       </c>
     </row>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すまない</t>
+          <t xml:space="preserve">……ごめん</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うむ</t>
+          <t xml:space="preserve">……ええ</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">autumnWarChampion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7759,14 +7759,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの試合のことは、ずっと体が覚えてる</t>
+          <t xml:space="preserve">みんなで勝ち取った勝利です。</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.standard.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[1]</t>
+          <t xml:space="preserve">bestMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7791,14 +7791,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この重さを、背負い続ける</t>
+          <t xml:space="preserve">……あの試合のことは、ずっと体が覚えてる</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.standard.quiet[1]</t>
+          <t xml:space="preserve">champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7823,14 +7823,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。この場所が、わたしの全部だった</t>
+          <t xml:space="preserve">……この重さを、背負い続ける</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.standard.quiet[1]</t>
+          <t xml:space="preserve">hallOfFame.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7855,14 +7855,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます</t>
+          <t xml:space="preserve">……ありがとう。この場所が、私の全部だった</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.standard.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.standard.quiet[1]</t>
+          <t xml:space="preserve">mediaAward.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7887,14 +7887,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一試合、一試合。それだけをやった</t>
+          <t xml:space="preserve">…ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.standard.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.standard.quiet[1]</t>
+          <t xml:space="preserve">mvp.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7919,14 +7919,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ何も成し遂げていない。これから</t>
+          <t xml:space="preserve">……一試合、一試合。それだけをやった</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">rookie.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7951,14 +7951,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドーム、ですか</t>
+          <t xml:space="preserve">……まだ何も成し遂げていない。これから</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">springTagChampion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7983,14 +7983,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やります</t>
+          <t xml:space="preserve">ふたりで積み上げた結果です。うれしいです。</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.quiet[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[3]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8015,14 +8015,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(無言で頷く)</t>
+          <t xml:space="preserve">…ドーム、ですか</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8047,14 +8047,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員でした</t>
+          <t xml:space="preserve">…やります</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8079,14 +8079,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、ございます</t>
+          <t xml:space="preserve">……（無言で頷く）</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.quiet[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[3]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8111,14 +8111,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(深く頭を下げる)</t>
+          <t xml:space="preserve">…満員でした</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8128,29 +8128,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……少し、手応えがある</t>
+          <t xml:space="preserve">…ありがとう、ございます</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8160,29 +8160,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いい人たちだと、思います</t>
+          <t xml:space="preserve">……（深く頭を下げる）</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.standard.quiet[1]</t>
+          <t xml:space="preserve">N1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8207,14 +8207,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……少し、休みます</t>
+          <t xml:space="preserve">……少し、手応えがある</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.standard.quiet[1]</t>
+          <t xml:space="preserve">N2.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8239,14 +8239,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……応援、ありがとうございます</t>
+          <t xml:space="preserve">……いい人たちだと、思います</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.standard.quiet[1]</t>
+          <t xml:space="preserve">N3.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8271,14 +8271,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（何も言わず、目を逸らす）</t>
+          <t xml:space="preserve">……少し、休みます</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.standard.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.standard.quiet[1]</t>
+          <t xml:space="preserve">N4.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8303,14 +8303,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この場所に感謝している</t>
+          <t xml:space="preserve">……応援、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8320,29 +8320,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.standard.quiet[1]</t>
+          <t xml:space="preserve">N5_low.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（何も言わず、封筒を見つめている）</t>
+          <t xml:space="preserve">………（何も言わず、目を逸らす）</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.quiet[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8352,29 +8352,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.quiet[1]</t>
+          <t xml:space="preserve">breakthrough.voice.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとうございます</t>
+          <t xml:space="preserve">…この場所に感謝している</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.quiet[1]</t>
+          <t xml:space="preserve">bonus_insult.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8399,14 +8399,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……頑張ります</t>
+          <t xml:space="preserve">…………（何も言わず、封筒を見つめている）</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.standard.quiet[1]</t>
+          <t xml:space="preserve">bonus.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8431,14 +8431,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ずっと、見てくれてたんですね</t>
+          <t xml:space="preserve">……ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.quiet[1]</t>
+          <t xml:space="preserve">camp.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8463,14 +8463,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ありがとう、ございます</t>
+          <t xml:space="preserve">……頑張ります</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.quiet[1]</t>
+          <t xml:space="preserve">encourage_high_trust.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8495,14 +8495,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう、ですか</t>
+          <t xml:space="preserve">……ずっと、見てくれてたんですね</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.quiet[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.quiet[2]</t>
+          <t xml:space="preserve">encourage.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8527,14 +8527,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……はい。わかりました</t>
+          <t xml:space="preserve">………ありがとう、ございます</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.standard.quiet[1]</t>
+          <t xml:space="preserve">faction_decree.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8559,14 +8559,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…が、頑張ります</t>
+          <t xml:space="preserve">……そう、ですか</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.quiet[1]</t>
+          <t xml:space="preserve">faction_decree.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8591,14 +8591,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……楽しかったです（小さく微笑んでいる）</t>
+          <t xml:space="preserve">……はい。わかりました</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.standard.quiet[1]</t>
+          <t xml:space="preserve">media.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8623,14 +8623,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し、休みます。ありがとうございます</t>
+          <t xml:space="preserve">…が、頑張ります</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.standard.quiet[1]</t>
+          <t xml:space="preserve">party.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8655,14 +8655,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。早く、戻ります</t>
+          <t xml:space="preserve">……楽しかったです（小さく微笑んでいる）</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.standard.quiet[1]</t>
+          <t xml:space="preserve">refresh_leave.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8687,14 +8687,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全力で、学びます</t>
+          <t xml:space="preserve">…少し、休みます。ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.standard.quiet[1]</t>
+          <t xml:space="preserve">special_treatment.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8719,14 +8719,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出演のお話、ですか…頑張ります</t>
+          <t xml:space="preserve">…ありがとうございます。早く、戻ります</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.standard.quiet[1]</t>
+          <t xml:space="preserve">trainer.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………他から、話が（小さな声で）</t>
+          <t xml:space="preserve">……全力で、学びます</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.quiet[1]</t>
+          <t xml:space="preserve">E1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8783,14 +8783,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（黙って道場を出ていこうとしている）</t>
+          <t xml:space="preserve">…出演のお話、ですか…頑張ります</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.quiet[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.quiet[2]</t>
+          <t xml:space="preserve">E6.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8815,14 +8815,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません…今日は……</t>
+          <t xml:space="preserve">………他から、話が（小さな声で）</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.standard.quiet[1]</t>
+          <t xml:space="preserve">S_boycott.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8847,14 +8847,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（黙っているが、その沈黙がかえって周囲を不安にさせている）</t>
+          <t xml:space="preserve">…………（黙って道場を出ていこうとしている）</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.standard.quiet[1]</t>
+          <t xml:space="preserve">S_boycott.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8879,14 +8879,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「…」とだけ投稿。ファンの間で憶測が広がっている）</t>
+          <t xml:space="preserve">……すみません…今日は……</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.standard.quiet[1]</t>
+          <t xml:space="preserve">S_grumble.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8911,14 +8911,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……挑戦させてください</t>
+          <t xml:space="preserve">（黙っているが、その沈黙がかえって周囲を不安にさせている）</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.standard.quiet[1]</t>
+          <t xml:space="preserve">S_sns.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8943,14 +8943,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの人と、戦わせてください</t>
+          <t xml:space="preserve">（SNSに「…」とだけ投稿。ファンの間で憶測が広がっている）</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.standard.quiet[1]</t>
+          <t xml:space="preserve">S1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8975,14 +8975,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……少し、休ませてください</t>
+          <t xml:space="preserve">……挑戦させてください</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.standard.quiet[1]</t>
+          <t xml:space="preserve">S2.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9007,14 +9007,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（険しい目でこちらを見つめている）</t>
+          <t xml:space="preserve">……あの人と、戦わせてください</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.standard.quiet[1]</t>
+          <t xml:space="preserve">S3.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9039,14 +9039,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（小さくため息をつき、視線を逸らす）</t>
+          <t xml:space="preserve">……少し、休ませてください</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.standard.quiet[1]</t>
+          <t xml:space="preserve">S4_direct.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9071,14 +9071,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……特訓、させてください</t>
+          <t xml:space="preserve">………（険しい目でこちらを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.standard.quiet[1]</t>
+          <t xml:space="preserve">S4_silent.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9103,14 +9103,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……後輩に、伝えたいことがあるんです</t>
+          <t xml:space="preserve">…………（小さくため息をつき、視線を逸らす）</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.standard.quiet[1]</t>
+          <t xml:space="preserve">S5.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9135,14 +9135,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出る。頑張る</t>
+          <t xml:space="preserve">……特訓、させてください</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.standard.quiet[1]</t>
+          <t xml:space="preserve">S6.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9167,14 +9167,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……わたしで、いいんですか。……やります</t>
+          <t xml:space="preserve">……後輩に、伝えたいことがあるんです</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.standard.quiet[1]</t>
+          <t xml:space="preserve">E1.accept.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9199,14 +9199,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません</t>
+          <t xml:space="preserve">……出る。頑張る</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.standard.quiet[1]</t>
+          <t xml:space="preserve">E1.recommend.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9231,14 +9231,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………あの人とは、もう…</t>
+          <t xml:space="preserve">……私で、いいんですか。……やります</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.standard.quiet[1]</t>
+          <t xml:space="preserve">B1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9263,14 +9263,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに俯いている）</t>
+          <t xml:space="preserve">……すみません</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.standard.quiet[1]</t>
+          <t xml:space="preserve">B2_fighter1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9295,14 +9295,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかりました。やります</t>
+          <t xml:space="preserve">………あの人とは、もう…</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.standard.quiet[1]</t>
+          <t xml:space="preserve">B2_fighter2.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9327,14 +9327,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やります</t>
+          <t xml:space="preserve">………（静かに俯いている）</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.standard.quiet[1]</t>
+          <t xml:space="preserve">B4_brand.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9359,14 +9359,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンの人たちと話す。ちゃんとやります</t>
+          <t xml:space="preserve">…わかりました。やります</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.standard.quiet[1]</t>
+          <t xml:space="preserve">B4_cm.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9391,14 +9391,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…歩けばいいんですね。やります</t>
+          <t xml:space="preserve">…やります</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.standard.quiet[1]</t>
+          <t xml:space="preserve">B4_fan.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9423,14 +9423,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…撮るだけですよね。わかりました</t>
+          <t xml:space="preserve">…ファンの人たちと話す。ちゃんとやります</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.standard.quiet[1]</t>
+          <t xml:space="preserve">B4_fashion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9455,14 +9455,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…喋るんですか。少し、緊張します</t>
+          <t xml:space="preserve">…歩けばいいんですね。やります</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.standard.quiet[1]</t>
+          <t xml:space="preserve">B4_gravure.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9487,14 +9487,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…がんばります</t>
+          <t xml:space="preserve">…撮るだけですよね。わかりました</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9504,29 +9504,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">B4_variety.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………よろしくお願いします</t>
+          <t xml:space="preserve">…喋るんですか。少し、緊張します</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9536,29 +9536,29 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">B4.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくお願いします</t>
+          <t xml:space="preserve">…がんばります</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9583,14 +9583,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………(深々と一礼)</t>
+          <t xml:space="preserve">………よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.quiet[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[3]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9615,14 +9615,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全力でやります</t>
+          <t xml:space="preserve">…よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9647,14 +9647,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくお願いします</t>
+          <t xml:space="preserve">………（深々と一礼）</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9679,14 +9679,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくお願いします</t>
+          <t xml:space="preserve">……全力でやります</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9696,12 +9696,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9711,14 +9711,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…(静かに頭を下げる)</t>
+          <t xml:space="preserve">…よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.quiet[3]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9728,12 +9728,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[3]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9743,14 +9743,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめん</t>
+          <t xml:space="preserve">…よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9775,14 +9775,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（終わったはずの相手を、じっと見ている）</t>
+          <t xml:space="preserve">…（静かに頭を下げる）</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9792,12 +9792,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9807,14 +9807,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（あの日の敗北の瞬間が、まだ耳から抜けない）</t>
+          <t xml:space="preserve">…ごめん</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.standard.quiet[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9839,14 +9839,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………よろしくお願いします</t>
+          <t xml:space="preserve">………（終わったはずの相手を、じっと見ている）</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9861,7 +9861,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.quiet[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9871,14 +9871,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくお願いします</t>
+          <t xml:space="preserve">………（あの日の敗北の瞬間が、まだ耳から抜けない）</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.quiet[2]</t>
+          <t xml:space="preserve">draftInterest.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9903,14 +9903,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………(深々と一礼)</t>
+          <t xml:space="preserve">………よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.quiet[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.quiet[3]</t>
+          <t xml:space="preserve">draftJoin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9935,14 +9935,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全力でやります</t>
+          <t xml:space="preserve">…よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.quiet[1]</t>
+          <t xml:space="preserve">draftJoin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9967,14 +9967,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう一度、リングに立てるんですね</t>
+          <t xml:space="preserve">………（深々と一礼）</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.quiet[2]</t>
+          <t xml:space="preserve">draftJoin.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -9999,14 +9999,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…声がかかって、よかったです</t>
+          <t xml:space="preserve">……全力でやります</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.standard.quiet[1]</t>
+          <t xml:space="preserve">faGreeting.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10031,14 +10031,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくお願いします</t>
+          <t xml:space="preserve">…もう一度、リングに立てるんですね</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.standard.quiet[1]</t>
+          <t xml:space="preserve">faGreeting.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10063,14 +10063,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくお願いします</t>
+          <t xml:space="preserve">…声がかかって、よかったです</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.standard.quiet[1]</t>
+          <t xml:space="preserve">faSigning.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10095,14 +10095,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が、軽いです。…今日は、いけます</t>
+          <t xml:space="preserve">…よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.standard.quiet[1]</t>
+          <t xml:space="preserve">faWelcome.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10127,14 +10127,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が、重いです。…今日は、たぶん、残りません</t>
+          <t xml:space="preserve">…よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.standard.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10159,14 +10159,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…同じことを、しているのに。…返るものが、少ない</t>
+          <t xml:space="preserve">…体が、軽いです。…今日は、いけます</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.quiet[2]</t>
+          <t xml:space="preserve">heatSelf.heavy.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10191,14 +10191,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…(静かに頭を下げる)</t>
+          <t xml:space="preserve">…体が、重いです。…今日は、たぶん、残りません</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.quiet[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.quiet[3]</t>
+          <t xml:space="preserve">heatSelf.warm.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10223,14 +10223,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめん</t>
+          <t xml:space="preserve">…同じことを、しているのに。…返るものが、少ない</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.quiet[1]</t>
+          <t xml:space="preserve">injury.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10255,14 +10255,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(深く一礼)</t>
+          <t xml:space="preserve">…（静かに頭を下げる）</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.quiet[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.quiet[3]</t>
+          <t xml:space="preserve">injury.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10287,14 +10287,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お世話になりました</t>
+          <t xml:space="preserve">…ごめん</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.standard.quiet[1]</t>
+          <t xml:space="preserve">release.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10319,14 +10319,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間ですが、よろしくお願いします</t>
+          <t xml:space="preserve">……（深く一礼）</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.quiet[1]</t>
+          <t xml:space="preserve">release.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10351,14 +10351,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていてくれた人が、いたんですね</t>
+          <t xml:space="preserve">…お世話になりました</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.quiet[2]</t>
+          <t xml:space="preserve">rentalGreeting.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10383,14 +10383,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…がんばります。…それだけ、です</t>
+          <t xml:space="preserve">…短い間ですが、よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.standard.quiet[1]</t>
+          <t xml:space="preserve">scoutGreeting.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10415,14 +10415,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（唇を噛んでいる）</t>
+          <t xml:space="preserve">…見ていてくれた人が、いたんですね</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.standard.quiet[1]</t>
+          <t xml:space="preserve">scoutGreeting.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10447,14 +10447,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">…がんばります。…それだけ、です</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.standard.quiet[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10479,14 +10479,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今は…一人にしてください</t>
+          <t xml:space="preserve">………（唇を噛んでいる）</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.quiet[1]</t>
+          <t xml:space="preserve">titleDefense.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10511,14 +10511,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトを抱きしめている）</t>
+          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10528,12 +10528,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">titleLoss.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10543,14 +10543,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(深く一礼)</t>
+          <t xml:space="preserve">……今は…一人にしてください</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.quiet[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10560,12 +10560,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[3]</t>
+          <t xml:space="preserve">titleWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10575,14 +10575,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お世話になりました</t>
+          <t xml:space="preserve">………（ベルトを抱きしめている）</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
@@ -10607,14 +10607,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間ですが、よろしくお願いします</t>
+          <t xml:space="preserve">……（深く一礼）</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10639,14 +10639,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（唇を噛んでいる）</t>
+          <t xml:space="preserve">…お世話になりました</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
@@ -10671,14 +10671,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">…短い間ですが、よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
@@ -10703,14 +10703,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今は…一人にしてください</t>
+          <t xml:space="preserve">………（唇を噛んでいる）</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
@@ -10735,14 +10735,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトを抱きしめている）</t>
+          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10752,29 +10752,29 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.quiet.standard[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、終わりだ</t>
+          <t xml:space="preserve">……今は…一人にしてください</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10784,29 +10784,29 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.standard[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……遠くなった</t>
+          <t xml:space="preserve">………（ベルトを抱きしめている）</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.standard[2]</t>
+          <t xml:space="preserve">bond_39_down.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10831,14 +10831,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……気づけば、隣にいない</t>
+          <t xml:space="preserve">……もう、終わりだ</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.standard[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10863,14 +10863,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最近、隣にいると落ち着く</t>
+          <t xml:space="preserve">……遠くなった</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.standard[2]</t>
+          <t xml:space="preserve">bond_59_down.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10895,14 +10895,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この距離が、静かで心地いい</t>
+          <t xml:space="preserve">……気づけば、隣にいない</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.standard[1]</t>
+          <t xml:space="preserve">bond_60_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10927,14 +10927,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……私の光だ</t>
+          <t xml:space="preserve">……最近、隣にいると落ち着く</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.standard[2]</t>
+          <t xml:space="preserve">bond_60_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10959,14 +10959,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そばにいてくれれば、それでいい</t>
+          <t xml:space="preserve">……この距離が、静かで心地いい</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10981,7 +10981,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.standard[1]</t>
+          <t xml:space="preserve">bond_80_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -10991,14 +10991,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、考えない</t>
+          <t xml:space="preserve">……私の光だ</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.standard[2]</t>
+          <t xml:space="preserve">bond_80_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11023,14 +11023,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……風が止んだ。そんな感覚だ</t>
+          <t xml:space="preserve">……そばにいてくれれば、それでいい</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.standard[1]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11055,14 +11055,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……考えてしまう。どうしても</t>
+          <t xml:space="preserve">……もう、考えない</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.standard[2]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11087,14 +11087,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……燃えている。自分の中の何かが</t>
+          <t xml:space="preserve">……風が止んだ。そんな感覚だ</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.standard[1]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11119,14 +11119,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認めたくないけど、意識してる</t>
+          <t xml:space="preserve">……考えてしまう。どうしても</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.standard[2]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11151,14 +11151,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そのことばかり考えている</t>
+          <t xml:space="preserve">……燃えている。自分の中の何かが</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.standard[1]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11183,14 +11183,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この相手がいる限り、リングに立ち続ける</t>
+          <t xml:space="preserve">……認めたくないけど、意識してる</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.standard[2]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11215,14 +11215,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……言葉はいらない。リングの上で語り合おう</t>
+          <t xml:space="preserve">……そのことばかり考えている</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.standard[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11247,14 +11247,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいたい。ずっと</t>
+          <t xml:space="preserve">……この相手がいる限り、リングに立ち続ける</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.standard[2]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11279,14 +11279,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この場所を、守りたい</t>
+          <t xml:space="preserve">……言葉はいらない。リングの上で語り合おう</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.standard[1]</t>
+          <t xml:space="preserve">trust_above_75.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11311,14 +11311,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（荷物をまとめ始めている）</t>
+          <t xml:space="preserve">……ここにいたい。ずっと</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.standard[2]</t>
+          <t xml:space="preserve">trust_above_75.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11343,14 +11343,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、何も感じない</t>
+          <t xml:space="preserve">……この場所を、守りたい</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.quiet.standard[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11375,14 +11375,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいていいのか、分からなくなってきた</t>
+          <t xml:space="preserve">……（荷物をまとめ始めている）</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11392,12 +11392,12 @@
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.quiet[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11407,14 +11407,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。でも…悪くなかった</t>
+          <t xml:space="preserve">……もう、何も感じない</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.quiet[1]</t>
+          <t xml:space="preserve">trust_below_35.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11439,14 +11439,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（小さくガッツポーズをしている）</t>
+          <t xml:space="preserve">……ここにいていいのか、分からなくなってきた</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11461,7 +11461,7 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11471,14 +11471,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いい試合だった。全てが噛み合った</t>
+          <t xml:space="preserve">……負けた。でも…悪くなかった</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11493,7 +11493,7 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11503,14 +11503,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（無言で拳を握りしめている）</t>
+          <t xml:space="preserve">……（小さくガッツポーズをしている）</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11535,14 +11535,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">……いい試合だった。全てが噛み合った</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-01.loss.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11567,14 +11567,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くない</t>
+          <t xml:space="preserve">……（無言で拳を握りしめている）</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-01.win.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11599,14 +11599,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（黙々とスクワットを続けている）</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-01.win.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11631,14 +11631,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（汗が床に落ちる音だけが響く）</t>
+          <t xml:space="preserve">……悪くない</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-02.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11663,14 +11663,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（不安そうに窓の外を見ている）</t>
+          <t xml:space="preserve">……（黙々とスクワットを続けている）</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-02.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11695,14 +11695,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいてもいいんだな</t>
+          <t xml:space="preserve">………（汗が床に落ちる音だけが響く）</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11727,14 +11727,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（そっと隣を見て、少し微笑んでいる）</t>
+          <t xml:space="preserve">……（不安そうに窓の外を見ている）</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11759,14 +11759,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（試合映像を食い入るように見ている）</t>
+          <t xml:space="preserve">……ここにいてもいいんだな</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-04.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11791,14 +11791,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（リングを見つめている）</t>
+          <t xml:space="preserve">……（そっと隣を見て、少し微笑んでいる）</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-05.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11823,14 +11823,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出番がない。ただそれだけが、重い</t>
+          <t xml:space="preserve">……（試合映像を食い入るように見ている）</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-06.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11855,14 +11855,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が、動かない</t>
+          <t xml:space="preserve">……（リングを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-06.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -11887,14 +11887,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（無言で練習を続けている）</t>
+          <t xml:space="preserve">……出番がない。ただそれだけが、重い</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-07.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -11919,14 +11919,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（壁に拳を押し当てている）</t>
+          <t xml:space="preserve">……体が、動かない</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-08.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -11951,14 +11951,14 @@
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いい流れだ。このまま</t>
+          <t xml:space="preserve">……（無言で練習を続けている）</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-08.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -11983,14 +11983,14 @@
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（天井を見つめている）</t>
+          <t xml:space="preserve">……（壁に拳を押し当てている）</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-09.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -12015,14 +12015,14 @@
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……リングが、遠い</t>
+          <t xml:space="preserve">……いい流れだ。このまま</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-10.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -12047,14 +12047,14 @@
       </c>
       <c r="F367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（視線は合わせない）</t>
+          <t xml:space="preserve">……（天井を見つめている）</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -12064,12 +12064,12 @@
       </c>
       <c r="C368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">GL-10.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -12079,14 +12079,14 @@
       </c>
       <c r="F368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふぅ。あの調子は続かないか</t>
+          <t xml:space="preserve">……リングが、遠い</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -12096,12 +12096,12 @@
       </c>
       <c r="C369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">GL-11.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -12111,14 +12111,14 @@
       </c>
       <c r="F369" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……元に戻った。でも…少し、違う自分になれた気がする</t>
+          <t xml:space="preserve">……（視線は合わせない）</t>
         </is>
       </c>
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -12128,29 +12128,29 @@
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F370" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、立ってる。最後まで、いく</t>
+          <t xml:space="preserve">……ふぅ。あの調子は続かないか</t>
         </is>
       </c>
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -12160,29 +12160,29 @@
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.quiet[2]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F371" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……身体は重い。でも、退かない</t>
+          <t xml:space="preserve">……元に戻った。でも…少し、違う自分になれた気がする</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -12197,7 +12197,7 @@
       </c>
       <c r="D372" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">preFinal.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
@@ -12207,14 +12207,14 @@
       </c>
       <c r="F372" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……相手は誰でもいい。倒す</t>
+          <t xml:space="preserve">……まだ、立ってる。最後まで、いく</t>
         </is>
       </c>
     </row>
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="D373" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.quiet[2]</t>
+          <t xml:space="preserve">preFinal.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E373" t="inlineStr" s="2">
@@ -12239,14 +12239,14 @@
       </c>
       <c r="F373" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……真っ向から。まだ、これから</t>
+          <t xml:space="preserve">……身体は重い。でも、退かない</t>
         </is>
       </c>
     </row>
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="D374" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.quiet[1]</t>
+          <t xml:space="preserve">preMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
@@ -12271,14 +12271,14 @@
       </c>
       <c r="F374" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、落とした。まだ立ってる。……次</t>
+          <t xml:space="preserve">……相手は誰でもいい。倒す</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="D375" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.quiet[2]</t>
+          <t xml:space="preserve">preMatch.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E375" t="inlineStr" s="2">
@@ -12303,14 +12303,14 @@
       </c>
       <c r="F375" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……息は上がってる。でも、退かない。……来い</t>
+          <t xml:space="preserve">……真っ向から。まだ、これから</t>
         </is>
       </c>
     </row>
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12320,12 +12320,12 @@
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[1]</t>
+          <t xml:space="preserve">survivor.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E376" t="inlineStr" s="2">
@@ -12335,14 +12335,14 @@
       </c>
       <c r="F376" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人で、最後まで残った。それが嬉しい</t>
+          <t xml:space="preserve">……一人、落とした。まだ立ってる。……次</t>
         </is>
       </c>
     </row>
     <row r="377" ht="40" customHeight="1">
       <c r="A377" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -12352,12 +12352,12 @@
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[2]</t>
+          <t xml:space="preserve">survivor.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E377" t="inlineStr" s="2">
@@ -12367,14 +12367,14 @@
       </c>
       <c r="F377" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人じゃなかった。だから、勝てた</t>
+          <t xml:space="preserve">……息は上がってる。でも、退かない。……来い</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="D378" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[3]</t>
+          <t xml:space="preserve">champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E378" t="inlineStr" s="2">
@@ -12399,14 +12399,14 @@
       </c>
       <c r="F378" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……仲間がいてくれた。それだけで十分</t>
+          <t xml:space="preserve">……三人で、最後まで残った。それが嬉しい</t>
         </is>
       </c>
     </row>
     <row r="379" ht="40" customHeight="1">
       <c r="A379" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="D379" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.quiet[1]</t>
+          <t xml:space="preserve">champion.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
@@ -12431,14 +12431,14 @@
       </c>
       <c r="F379" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった。次は、最後まで倒す</t>
+          <t xml:space="preserve">……一人じゃなかった。だから、勝てた</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="D380" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.quiet[2]</t>
+          <t xml:space="preserve">champion.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
@@ -12463,14 +12463,14 @@
       </c>
       <c r="F380" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……MVPでも、負けは負け。忘れない</t>
+          <t xml:space="preserve">……仲間がいてくれた。それだけで十分</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="D381" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.quiet[3]</t>
+          <t xml:space="preserve">defiant.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E381" t="inlineStr" s="2">
@@ -12495,14 +12495,14 @@
       </c>
       <c r="F381" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ終わってない。次がある</t>
+          <t xml:space="preserve">……足りなかった。次は、最後まで倒す</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="D382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.quiet[1]</t>
+          <t xml:space="preserve">defiant.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12527,14 +12527,14 @@
       </c>
       <c r="F382" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ立ってる。だから、私の勝ち</t>
+          <t xml:space="preserve">……MVPでも、負けは負け。忘れない</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="D383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.quiet[2]</t>
+          <t xml:space="preserve">defiant.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12559,14 +12559,14 @@
       </c>
       <c r="F383" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、また一人。気がついたら、最後だった</t>
+          <t xml:space="preserve">……まだ終わってない。次がある</t>
         </is>
       </c>
     </row>
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="D384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.quiet[3]</t>
+          <t xml:space="preserve">gauntlet.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12591,14 +12591,14 @@
       </c>
       <c r="F384" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……声は出ない。でも、足はまだ動いてる</t>
+          <t xml:space="preserve">……まだ立ってる。だから、私の勝ち</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12608,12 +12608,12 @@
       </c>
       <c r="C385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
@@ -12623,14 +12623,14 @@
       </c>
       <c r="F385" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">……一人、また一人。気がついたら、最後だった</t>
         </is>
       </c>
     </row>
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="C386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[2]</t>
+          <t xml:space="preserve">gauntlet.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
@@ -12655,14 +12655,14 @@
       </c>
       <c r="F386" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………………ありがとう</t>
+          <t xml:space="preserve">……声は出ない。でも、足はまだ動いてる</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12677,7 +12677,7 @@
       </c>
       <c r="D387" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.quiet[1]</t>
+          <t xml:space="preserve">champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E387" t="inlineStr" s="2">
@@ -12687,14 +12687,14 @@
       </c>
       <c r="F387" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………………（悔しそうに拳を握る）</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="D388" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.quiet[2]</t>
+          <t xml:space="preserve">champion.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12719,14 +12719,14 @@
       </c>
       <c r="F388" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、負けない</t>
+          <t xml:space="preserve">………………ありがとう</t>
         </is>
       </c>
     </row>
     <row r="389" ht="40" customHeight="1">
       <c r="A389" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="D389" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.quiet[1]</t>
+          <t xml:space="preserve">postLose.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
@@ -12751,14 +12751,14 @@
       </c>
       <c r="F389" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">………………（悔しそうに拳を握る）</t>
         </is>
       </c>
     </row>
     <row r="390" ht="40" customHeight="1">
       <c r="A390" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="D390" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.quiet[2]</t>
+          <t xml:space="preserve">postLose.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E390" t="inlineStr" s="2">
@@ -12783,14 +12783,14 @@
       </c>
       <c r="F390" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">……次は、負けない</t>
         </is>
       </c>
     </row>
     <row r="391" ht="40" customHeight="1">
       <c r="A391" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="D391" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.quiet[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="2">
@@ -12815,14 +12815,14 @@
       </c>
       <c r="F391" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……良い経験だった</t>
+          <t xml:space="preserve">……次</t>
         </is>
       </c>
     </row>
     <row r="392" ht="40" customHeight="1">
       <c r="A392" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="D392" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.quiet[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E392" t="inlineStr" s="2">
@@ -12847,14 +12847,14 @@
       </c>
       <c r="F392" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………………（満足げに頷く）</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="393" ht="40" customHeight="1">
       <c r="A393" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="D393" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.quiet[1]</t>
+          <t xml:space="preserve">postWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E393" t="inlineStr" s="2">
@@ -12879,14 +12879,14 @@
       </c>
       <c r="F393" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後の一試合</t>
+          <t xml:space="preserve">……良い経験だった</t>
         </is>
       </c>
     </row>
     <row r="394" ht="40" customHeight="1">
       <c r="A394" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="D394" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.quiet[2]</t>
+          <t xml:space="preserve">postWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="2">
@@ -12911,14 +12911,14 @@
       </c>
       <c r="F394" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全部、出す</t>
+          <t xml:space="preserve">………………（満足げに頷く）</t>
         </is>
       </c>
     </row>
     <row r="395" ht="40" customHeight="1">
       <c r="A395" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="D395" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">preFinal.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -12943,14 +12943,14 @@
       </c>
       <c r="F395" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やる</t>
+          <t xml:space="preserve">……最後の一試合</t>
         </is>
       </c>
     </row>
     <row r="396" ht="40" customHeight="1">
       <c r="A396" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="D396" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.quiet[1]</t>
+          <t xml:space="preserve">preFinal.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="2">
@@ -12975,14 +12975,14 @@
       </c>
       <c r="F396" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……わかった</t>
+          <t xml:space="preserve">……全部、出す</t>
         </is>
       </c>
     </row>
     <row r="397" ht="40" customHeight="1">
       <c r="A397" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="D397" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.quiet[2]</t>
+          <t xml:space="preserve">preMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E397" t="inlineStr" s="2">
@@ -13007,14 +13007,14 @@
       </c>
       <c r="F397" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出る</t>
+          <t xml:space="preserve">……やる</t>
         </is>
       </c>
     </row>
     <row r="398" ht="40" customHeight="1">
       <c r="A398" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
@@ -13024,12 +13024,12 @@
       </c>
       <c r="C398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D398" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">summon.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="2">
@@ -13039,14 +13039,14 @@
       </c>
       <c r="F398" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに構えている）</t>
+          <t xml:space="preserve">……わかった</t>
         </is>
       </c>
     </row>
     <row r="399" ht="40" customHeight="1">
       <c r="A399" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="C399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D399" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">summon.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -13071,14 +13071,14 @@
       </c>
       <c r="F399" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（リングの上で静かに涙を流す）</t>
+          <t xml:space="preserve">……出る</t>
         </is>
       </c>
     </row>
     <row r="400" ht="40" customHeight="1">
       <c r="A400" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -13088,12 +13088,12 @@
       </c>
       <c r="C400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D400" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="2">
@@ -13103,14 +13103,14 @@
       </c>
       <c r="F400" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ありがとう、ございます……（声が震えている）</t>
+          <t xml:space="preserve">……（静かに構えている）</t>
         </is>
       </c>
     </row>
     <row r="401" ht="40" customHeight="1">
       <c r="A401" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.quiet[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -13120,7 +13120,7 @@
       </c>
       <c r="C401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D401" t="inlineStr" s="12">
@@ -13135,14 +13135,14 @@
       </c>
       <c r="F401" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……対抗戦を申し込む</t>
+          <t xml:space="preserve">………（リングの上で静かに涙を流す）</t>
         </is>
       </c>
     </row>
     <row r="402" ht="40" customHeight="1">
       <c r="A402" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.quiet[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -13152,7 +13152,7 @@
       </c>
       <c r="C402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D402" t="inlineStr" s="12">
@@ -13167,14 +13167,14 @@
       </c>
       <c r="F402" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戦え</t>
+          <t xml:space="preserve">………ありがとう、ございます……（声が震えている）</t>
         </is>
       </c>
     </row>
     <row r="403" ht="40" customHeight="1">
       <c r="A403" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D403" t="inlineStr" s="12">
@@ -13199,14 +13199,14 @@
       </c>
       <c r="F403" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか</t>
+          <t xml:space="preserve">……対抗戦を申し込む</t>
         </is>
       </c>
     </row>
     <row r="404" ht="40" customHeight="1">
       <c r="A404" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.quiet[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="C404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D404" t="inlineStr" s="12">
@@ -13231,14 +13231,14 @@
       </c>
       <c r="F404" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次はない</t>
+          <t xml:space="preserve">……戦え</t>
         </is>
       </c>
     </row>
     <row r="405" ht="40" customHeight="1">
       <c r="A405" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
@@ -13248,12 +13248,12 @@
       </c>
       <c r="C405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D405" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E405" t="inlineStr" s="2">
@@ -13263,14 +13263,14 @@
       </c>
       <c r="F405" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悔しい</t>
+          <t xml:space="preserve">……そうか</t>
         </is>
       </c>
     </row>
     <row r="406" ht="40" customHeight="1">
       <c r="A406" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.quiet[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
@@ -13280,12 +13280,12 @@
       </c>
       <c r="C406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D406" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.quiet[2]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13295,14 +13295,14 @@
       </c>
       <c r="F406" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は負けない</t>
+          <t xml:space="preserve">……次はない</t>
         </is>
       </c>
     </row>
     <row r="407" ht="40" customHeight="1">
       <c r="A407" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="D407" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.quiet[1]</t>
+          <t xml:space="preserve">result_lose.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E407" t="inlineStr" s="2">
@@ -13327,14 +13327,14 @@
       </c>
       <c r="F407" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">……悔しい</t>
         </is>
       </c>
     </row>
     <row r="408" ht="40" customHeight="1">
       <c r="A408" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="C408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D408" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">result_lose.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
@@ -13359,14 +13359,14 @@
       </c>
       <c r="F408" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。団体の力を、証明できた</t>
+          <t xml:space="preserve">……次は負けない</t>
         </is>
       </c>
     </row>
     <row r="409" ht="40" customHeight="1">
       <c r="A409" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="C409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D409" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">result_win.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E409" t="inlineStr" s="2">
@@ -13391,14 +13391,14 @@
       </c>
       <c r="F409" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これがうちの実力</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="410" ht="40" customHeight="1">
       <c r="A410" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="D410" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[3]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E410" t="inlineStr" s="2">
@@ -13423,14 +13423,14 @@
       </c>
       <c r="F410" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……みんなの分も、背負って戦った</t>
+          <t xml:space="preserve">……勝った。団体の力を、証明できた</t>
         </is>
       </c>
     </row>
     <row r="411" ht="40" customHeight="1">
       <c r="A411" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -13440,29 +13440,29 @@
       </c>
       <c r="C411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D411" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F411" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ありがとうございました（静かに涙を流している）</t>
+          <t xml:space="preserve">……これがうちの実力</t>
         </is>
       </c>
     </row>
     <row r="412" ht="40" customHeight="1">
       <c r="A412" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -13472,29 +13472,29 @@
       </c>
       <c r="C412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D412" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F412" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう一度、リングに立てるんですね</t>
+          <t xml:space="preserve">……みんなの分も、背負って戦った</t>
         </is>
       </c>
     </row>
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13504,29 +13504,29 @@
       </c>
       <c r="C413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">fighter.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F413" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…声がかかって、よかったです</t>
+          <t xml:space="preserve">………ありがとうございました（静かに涙を流している）</t>
         </is>
       </c>
     </row>
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="C414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D414" t="inlineStr" s="12">
@@ -13551,44 +13551,108 @@
       </c>
       <c r="F414" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていてくれた人が、いたんですね</t>
+          <t xml:space="preserve">…もう一度、リングに立てるんですね</t>
         </is>
       </c>
     </row>
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…声がかかって、よかったです</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="40" customHeight="1">
+      <c r="A416" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…見ていてくれた人が、いたんですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="40" customHeight="1">
+      <c r="A417" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.quiet[2]</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr" s="2">
+      <c r="B417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr" s="12">
+      <c r="D417" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr" s="2">
+      <c r="E417" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr" s="3">
+      <c r="F417" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…がんばります。…それだけ、です</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H415"/>
+  <autoFilter ref="A1:H417"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×寡黙.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H417"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4182,7 +4182,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.standard.quiet[1]</t>
+          <t xml:space="preserve">decline_accept.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4207,14 +4207,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え……本当ですか……？ あ、ありがとうございます……！ 頑張ります……！</t>
+          <t xml:space="preserve">…いいわ、それで。…下がったぶん、身軽になったと思っておく。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.standard.quiet[1]</t>
+          <t xml:space="preserve">decline_hold.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4239,14 +4239,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">それだけでも……ありがたいです。ありがとうございます……。</t>
+          <t xml:space="preserve">…下げない、の。…変わってるわね、社長は。…なら、その額のぶんは働くわ。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.standard.quiet[1]</t>
+          <t xml:space="preserve">decline_open.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4271,14 +4271,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう、ですか……。分かりました……。</t>
+          <t xml:space="preserve">…そう。文句はないわ。自分がいちばん分かってたから。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.standard.quiet[1]</t>
+          <t xml:space="preserve">decline_strict.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4303,14 +4303,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの……社長、少しお時間いただけますか……。{tenure}その……お給料のことなんですけど……。</t>
+          <t xml:space="preserve">…全部持っていくのね。…わかった。…もう、話すことはないわ。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.standard.quiet[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.standard.quiet[2]</t>
+          <t xml:space="preserve">decline_voluntary_accept.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4335,14 +4335,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長、言いにくいんですけど……。{record}もう少しだけ……お願いできないかなって……。</t>
+          <t xml:space="preserve">…素直に下げたわね。…嫌いじゃないわ、そういうの。…また、上げさせるから。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.standard.quiet[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4367,14 +4367,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……はい……分かりました……。……すみません、変なこと言って……。</t>
+          <t xml:space="preserve">…下げないの。……こっちが折れた形ね。…わかった。その額に、体のほうを合わせるわ。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.standard.quiet[1]</t>
+          <t xml:space="preserve">decline_voluntary_open.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません。もう、限界なんです。……さようなら。</t>
+          <t xml:space="preserve">…社長。{tenure}私の値段、下げていいわ。…見合わないものを貰うのは、落ち着かないから。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.standard.quiet[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.standard.quiet[2]</t>
+          <t xml:space="preserve">raise_accept.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4431,14 +4431,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ずっと我慢してきたんです。でも、もう……。</t>
+          <t xml:space="preserve">え……本当ですか……？ あ、ありがとうございます……！ 頑張ります……！</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.standard.quiet[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.standard.quiet[3]</t>
+          <t xml:space="preserve">raise_negotiate_accept.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何も言わずに去ろうかと思ったけど、一応挨拶だけ。辞めます。</t>
+          <t xml:space="preserve">それだけでも……ありがたいです。ありがとうございます……。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.standard.quiet[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4495,14 +4495,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞いてくれるんですか……。{record}私……ここにいる意味が、分からなくなって……。</t>
+          <t xml:space="preserve">……そう、ですか……。分かりました……。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.standard.quiet[1]</t>
+          <t xml:space="preserve">raise_open.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4527,14 +4527,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの……社長……。{tenure}言いにくいんですけど……もう、ここを離れたいです……。</t>
+          <t xml:space="preserve">あの……社長、少しお時間いただけますか……。{tenure}その……お給料のことなんですけど……。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.standard.quiet[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.standard.quiet[2]</t>
+          <t xml:space="preserve">raise_open.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4559,14 +4559,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい……。{tenure}私がいなくても……変わらないと思うんです……。</t>
+          <t xml:space="preserve">……社長、言いにくいんですけど……。{record}もう少しだけ……お願いできないかなって……。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.standard.quiet[1]</t>
+          <t xml:space="preserve">raise_refuse.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとうございました。{tenure_farewell}{rivalry}……お世話になりました。</t>
+          <t xml:space="preserve">……はい……分かりました……。……すみません、変なこと言って……。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.standard.quiet[1]</t>
+          <t xml:space="preserve">sudden_departure.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4623,14 +4623,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんなさい……。ありがたいんですけど……もう、決めたんです……。</t>
+          <t xml:space="preserve">……すみません。もう、限界なんです。……さようなら。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.standard.quiet[1]</t>
+          <t xml:space="preserve">sudden_departure.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4655,14 +4655,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ……そこまでしてくれるんですか……？ ……もう少しだけ、頑張ってみます……。</t>
+          <t xml:space="preserve">……ずっと我慢してきたんです。でも、もう……。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.standard.quiet[1]</t>
+          <t xml:space="preserve">sudden_departure.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4687,14 +4687,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今は動けない。ここにいる</t>
+          <t xml:space="preserve">……何も言わずに去ろうかと思ったけど、一応挨拶だけ。辞めます。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.standard.quiet[1]</t>
+          <t xml:space="preserve">transfer_listen.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4719,14 +4719,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ここにいる</t>
+          <t xml:space="preserve">……聞いてくれるんですか……。{record}私……ここにいる意味が、分からなくなって……。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4736,12 +4736,12 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.standard.quiet[1]</t>
+          <t xml:space="preserve">transfer_open.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4751,14 +4751,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………話は聞く</t>
+          <t xml:space="preserve">あの……社長……。{tenure}言いにくいんですけど……もう、ここを離れたいです……。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.standard.quiet[1]</t>
+          <t xml:space="preserve">transfer_open.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4783,14 +4783,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……行く。よろしく</t>
+          <t xml:space="preserve">……ごめんなさい……。{tenure}私がいなくても……変わらないと思うんです……。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4800,29 +4800,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.standard.quiet[1]</t>
+          <t xml:space="preserve">transfer_release.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、私たちのメンバーを、ちゃんと見てもらえるとありがたいです。</t>
+          <t xml:space="preserve">……ありがとうございました。{tenure_farewell}{rivalry}……お世話になりました。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4832,29 +4832,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.standard.quiet[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、次のメイン、私たちで挑ませてもらえませんか。</t>
+          <t xml:space="preserve">……ごめんなさい……。ありがたいんですけど……もう、決めたんです……。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.standard.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4864,29 +4864,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.standard.quiet[1]</t>
+          <t xml:space="preserve">transfer_retain_success.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、待遇のことで相談があります。私たちのメンバーのことです。</t>
+          <t xml:space="preserve">えっ……そこまでしてくれるんですか……？ ……もう少しだけ、頑張ってみます……。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.standard.quiet[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4896,29 +4896,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.standard.quiet[1]</t>
+          <t xml:space="preserve">blocked.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、私たちの仕事、見てもらえてますか。</t>
+          <t xml:space="preserve">…今は動けない。ここにいる</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.standard.quiet[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4928,29 +4928,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.standard.quiet[1]</t>
+          <t xml:space="preserve">fail.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…見てもらえてるんだ、って、安心しました。</t>
+          <t xml:space="preserve">………ここにいる</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.standard.quiet[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4960,29 +4960,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.standard.quiet[1]</t>
+          <t xml:space="preserve">start.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、すみません。出過ぎたことを言いました。</t>
+          <t xml:space="preserve">………話は聞く</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.standard.quiet[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4992,29 +4992,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.standard.quiet[1]</t>
+          <t xml:space="preserve">success.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちでしたか。</t>
+          <t xml:space="preserve">……行く。よろしく</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.standard.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5039,14 +5039,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。やります。</t>
+          <t xml:space="preserve">…社長、私たちのメンバーを、ちゃんと見てもらえるとありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.standard.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5071,14 +5071,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…社長、次のメイン、私たちで挑ませてもらえませんか。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.standard.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5103,14 +5103,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですね。ありがとうございます。</t>
+          <t xml:space="preserve">…社長、待遇のことで相談があります。私たちのメンバーのことです。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.standard.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5135,14 +5135,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。みんな、喜びます。</t>
+          <t xml:space="preserve">…社長、私たちの仕事、見てもらえてますか。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5167,14 +5167,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…ありがとうございます。…見てもらえてるんだ、って、安心しました。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5199,14 +5199,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくださって、嬉しいです。</t>
+          <t xml:space="preserve">…はい、すみません。出過ぎたことを言いました。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5231,14 +5231,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…見てもらえてたんですね。</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちでしたか。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5263,14 +5263,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。</t>
+          <t xml:space="preserve">…ありがとうございます。やります。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5295,14 +5295,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちで返してくださるんですね。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5327,14 +5327,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、すみません。…悪気は、なかったんですけど。</t>
+          <t xml:space="preserve">…そうですね。ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5359,14 +5359,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…でも、少し、考えます。</t>
+          <t xml:space="preserve">…ありがとうございます。みんな、喜びます。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5391,14 +5391,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、すみません。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5423,14 +5423,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい。</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで気にかけてくださって、嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5455,14 +5455,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。…やりすぎ、でしたね。</t>
+          <t xml:space="preserve">…ありがとうございます。…見てもらえてたんですね。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5487,14 +5487,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…ヒールの仕事、続けます。</t>
+          <t xml:space="preserve">…はい、わかりました。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5519,14 +5519,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。…出ます、ちゃんと。</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで返してくださるんですね。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5551,14 +5551,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…気を遣っていただいて。</t>
+          <t xml:space="preserve">…はい、すみません。…悪気は、なかったんですけど。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5583,14 +5583,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…私の代わりに、みんなを見てくださって。</t>
+          <t xml:space="preserve">…ありがとうございます。…でも、少し、考えます。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5615,14 +5615,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…少し、休みます。</t>
+          <t xml:space="preserve">…はい、すみません。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5647,14 +5647,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、平気です。</t>
+          <t xml:space="preserve">…はい。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5679,14 +5679,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…メンバーが受け止めてくれると、助かります。</t>
+          <t xml:space="preserve">…はい、わかりました。…やりすぎ、でしたね。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5711,14 +5711,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、…わかりました。気をつけます。</t>
+          <t xml:space="preserve">…ありがとうございます。…ヒールの仕事、続けます。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5743,14 +5743,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、ありがとうございます。</t>
+          <t xml:space="preserve">…申し訳ありません。…出ます、ちゃんと。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5775,14 +5775,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…下の子のフォロー、助かります。</t>
+          <t xml:space="preserve">…ありがとうございます。…気を遣っていただいて。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5807,14 +5807,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、すみません。</t>
+          <t xml:space="preserve">…ありがとうございます。…私の代わりに、みんなを見てくださって。</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5839,14 +5839,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…何も言わず、目を伏せた）</t>
+          <t xml:space="preserve">…ありがとうございます。…少し、休みます。</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5871,14 +5871,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、ありがとうございます。</t>
+          <t xml:space="preserve">…はい、平気です。</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5903,14 +5903,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、…わかりました。やりすぎ、だったかもしれません。</t>
+          <t xml:space="preserve">…ありがとうございます。…メンバーが受け止めてくれると、助かります。</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5935,14 +5935,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…見守ってください。</t>
+          <t xml:space="preserve">…はい、…わかりました。気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5967,14 +5967,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…下の子、限界が近かったかもしれません。</t>
+          <t xml:space="preserve">…はい、ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.quiet.attack.standard</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.attack.standard</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5999,14 +5999,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、戻れません</t>
+          <t xml:space="preserve">…ありがとうございます。…下の子のフォロー、助かります。</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.quiet.defend.standard</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.defend.standard</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6031,29 +6031,29 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そちらが望むなら</t>
+          <t xml:space="preserve">…はい、すみません。</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6063,29 +6063,29 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、ついていけない。</t>
+          <t xml:space="preserve">（…何も言わず、目を伏せた）</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6095,29 +6095,29 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……息が、できない。</t>
+          <t xml:space="preserve">…はい、ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6127,29 +6127,29 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……意外と、普通に、話せるね。</t>
+          <t xml:space="preserve">…はい、…わかりました。やりすぎ、だったかもしれません。</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6159,29 +6159,29 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、逃げない。</t>
+          <t xml:space="preserve">…ありがとうございます。…見守ってください。</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.quiet.hp_high[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.hp_high[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6191,29 +6191,29 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた、けど……組は、潰れない</t>
+          <t xml:space="preserve">…ありがとうございます。…下の子、限界が近かったかもしれません。</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.quiet.hp_high[2]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.attack.standard</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.hp_high[2]</t>
+          <t xml:space="preserve">quiet.attack.standard</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6223,29 +6223,29 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、ない、なんて……思ってない</t>
+          <t xml:space="preserve">……もう、戻れません</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.quiet.hp_low[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.defend.standard</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.hp_low[1]</t>
+          <t xml:space="preserve">quiet.defend.standard</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6255,14 +6255,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（沈黙）</t>
+          <t xml:space="preserve">そちらが望むなら</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.quiet.hp_mid[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.hp_mid[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6287,14 +6287,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……</t>
+          <t xml:space="preserve">……もう、ついていけない。</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6319,14 +6319,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">……息が、できない。</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.quiet.high[2]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[2]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これで、終わり。じゃない</t>
+          <t xml:space="preserve">……意外と、普通に、話せるね。</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.quiet.low[1]</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.low[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6383,14 +6383,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（深く息をつく）</t>
+          <t xml:space="preserve">……もう、逃げない。</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.quiet.mid[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.quiet.hp_high[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.mid[1]</t>
+          <t xml:space="preserve">standard.quiet.hp_high[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6415,14 +6415,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝てた</t>
+          <t xml:space="preserve">……負けた、けど……組は、潰れない</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.quiet.hp_high[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6432,12 +6432,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[1]</t>
+          <t xml:space="preserve">standard.quiet.hp_high[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6447,14 +6447,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……話すことは、もうない</t>
+          <t xml:space="preserve">……次は、ない、なんて……思ってない</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.high[2]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.quiet.hp_low[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[2]</t>
+          <t xml:space="preserve">standard.quiet.hp_low[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6479,14 +6479,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……行こう。リングが、待ってる</t>
+          <t xml:space="preserve">（沈黙）</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.high[3]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.quiet.hp_mid[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[3]</t>
+          <t xml:space="preserve">standard.quiet.hp_mid[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6511,14 +6511,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うちの組のこと、悪く言う声は、ぜんぶ今日で消す</t>
+          <t xml:space="preserve">……っ……</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.low[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.low[1]</t>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6543,14 +6543,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん。受けて立つ</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.mid[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.quiet.high[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.mid[1]</t>
+          <t xml:space="preserve">standard.quiet.high[2]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6575,14 +6575,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……来なよ</t>
+          <t xml:space="preserve">……これで、終わり。じゃない</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.quiet.low[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[1]</t>
+          <t xml:space="preserve">standard.quiet.low[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6607,14 +6607,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……分かった。リングで</t>
+          <t xml:space="preserve">……（深く息をつく）</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.quiet.high[2]</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.quiet.mid[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[2]</t>
+          <t xml:space="preserve">standard.quiet.mid[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6639,14 +6639,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん。逃げない</t>
+          <t xml:space="preserve">……勝てた</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.quiet.low[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.low[1]</t>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6671,14 +6671,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……分かった</t>
+          <t xml:space="preserve">……話すことは、もうない</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.quiet.mid[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.high[2]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.mid[1]</t>
+          <t xml:space="preserve">standard.quiet.high[2]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6703,14 +6703,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいよ</t>
+          <t xml:space="preserve">……行こう。リングが、待ってる</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES.standard.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.high[3]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[1]</t>
+          <t xml:space="preserve">standard.quiet.high[3]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6735,14 +6735,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。それだけ</t>
+          <t xml:space="preserve">……うちの組のこと、悪く言う声は、ぜんぶ今日で消す</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.standard.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.low[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[1]</t>
+          <t xml:space="preserve">standard.quiet.low[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6767,14 +6767,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">……うん。受けて立つ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES.standard.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.quiet.mid[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[1]</t>
+          <t xml:space="preserve">standard.quiet.mid[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6799,14 +6799,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめん</t>
+          <t xml:space="preserve">……来なよ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.standard.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
@@ -6831,14 +6831,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">……分かった。リングで</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES.standard.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.quiet.high[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[1]</t>
+          <t xml:space="preserve">standard.quiet.high[2]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6863,14 +6863,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……行く</t>
+          <t xml:space="preserve">……うん。逃げない</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.quiet.low[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6880,12 +6880,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[1]</t>
+          <t xml:space="preserve">standard.quiet.low[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6895,14 +6895,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今夜で、終わらせる</t>
+          <t xml:space="preserve">……分かった</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.standard.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.quiet.mid[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[1]</t>
+          <t xml:space="preserve">standard.quiet.mid[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6927,14 +6927,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいよ。来な</t>
+          <t xml:space="preserve">……いいよ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.quiet.hp_high[1]</t>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES.standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.hp_high[1]</t>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6959,14 +6959,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた</t>
+          <t xml:space="preserve">……負けた。それだけ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.quiet.hp_mid[1]</t>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.hp_mid[1]</t>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6991,14 +6991,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ええ</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES.standard.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES.standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
@@ -7023,14 +7023,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。それだけ</t>
+          <t xml:space="preserve">……ごめん</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
@@ -7055,14 +7055,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……時間だ</t>
+          <t xml:space="preserve">……次</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.quiet.high[2]</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES.standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet.high[2]</t>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7087,14 +7087,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……席を、もらいに来た</t>
+          <t xml:space="preserve">……行く</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.standard.quiet.high[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
@@ -7119,238 +7119,238 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいだろう</t>
+          <t xml:space="preserve">……今夜で、終わらせる</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何かが、変わった</t>
+          <t xml:space="preserve">……いいよ。来な</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.quiet.hp_high[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet.hp_high[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…見える。次の一手が、はっきりと）</t>
+          <t xml:space="preserve">……負けた</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.quiet.hp_mid[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">standard.quiet.hp_mid[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…体が、勝手に動いている——）</t>
+          <t xml:space="preserve">……ええ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.standard.quiet[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES.standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が、軽いです。…今日は、いけます</t>
+          <t xml:space="preserve">……勝った。それだけ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.standard.quiet[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が、重いです。…今日は、たぶん、残りません</t>
+          <t xml:space="preserve">……時間だ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.standard.quiet[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.quiet.high[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet.high[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…同じことを、しているのに。…返るものが、少ない</t>
+          <t xml:space="preserve">……席を、もらいに来た</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.standard.quiet[1]</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet.high[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに息をつく）…ここまで、か</t>
+          <t xml:space="preserve">……いいだろう</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.standard.quiet[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7375,14 +7375,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ここまで来た</t>
+          <t xml:space="preserve">……何かが、変わった</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.standard.quiet[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7407,14 +7407,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……少し、強くなれた</t>
+          <t xml:space="preserve">（…見える。次の一手が、はっきりと）</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.standard.quiet[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7439,14 +7439,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（静かに拳を握る）</t>
+          <t xml:space="preserve">（…体が、勝手に動いている——）</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.standard.quiet[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.standard.quiet[1]</t>
+          <t xml:space="preserve">fresh.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7471,14 +7471,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……見てくれてる人が、いるんだ</t>
+          <t xml:space="preserve">…体が、軽いです。…今日は、いけます</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.standard.quiet[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.standard.quiet[1]</t>
+          <t xml:space="preserve">heavy.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7503,14 +7503,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……こんなに……ありがとう</t>
+          <t xml:space="preserve">…体が、重いです。…今日は、たぶん、残りません</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7520,12 +7520,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">warm.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7535,14 +7535,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……闘う理由が、見えない</t>
+          <t xml:space="preserve">…同じことを、しているのに。…返るものが、少ない</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">cap_reached.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう一度、闘える</t>
+          <t xml:space="preserve">………（静かに息をつく）…ここまで、か</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">ovr_elite.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻ってきた</t>
+          <t xml:space="preserve">………ここまで来た</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.standard.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.standard.quiet[1]</t>
+          <t xml:space="preserve">ovr_growth.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7631,14 +7631,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの負けから、動けない</t>
+          <t xml:space="preserve">……少し、強くなれた</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.standard.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.standard.quiet[1]</t>
+          <t xml:space="preserve">ovr_legend.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7663,14 +7663,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体は治った。でも、何か違う</t>
+          <t xml:space="preserve">…………（静かに拳を握る）</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.standard.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.standard.quiet[1]</t>
+          <t xml:space="preserve">pop_growth.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7695,14 +7695,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……リングが、遠い</t>
+          <t xml:space="preserve">……見てくれてる人が、いるんだ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.standard.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.standard.quiet[1]</t>
+          <t xml:space="preserve">pop_star.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7727,14 +7727,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……治った。でも、心は</t>
+          <t xml:space="preserve">……こんなに……ありがとう</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.standard.quiet[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7744,29 +7744,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで勝ち取った勝利です。</t>
+          <t xml:space="preserve">……闘う理由が、見えない</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7776,29 +7776,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの試合のことは、ずっと体が覚えてる</t>
+          <t xml:space="preserve">……もう一度、闘える</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.standard.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7808,29 +7808,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この重さを、背負い続ける</t>
+          <t xml:space="preserve">……戻ってきた</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7840,29 +7840,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.standard.quiet[1]</t>
+          <t xml:space="preserve">defeat.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。この場所が、私の全部だった</t>
+          <t xml:space="preserve">……あの負けから、動けない</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7872,29 +7872,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.standard.quiet[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます</t>
+          <t xml:space="preserve">……体は治った。でも、何か違う</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.standard.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7904,29 +7904,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.standard.quiet[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一試合、一試合。それだけをやった</t>
+          <t xml:space="preserve">……リングが、遠い</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.standard.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7936,29 +7936,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.standard.quiet[1]</t>
+          <t xml:space="preserve">penalty_end.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ何も成し遂げていない。これから</t>
+          <t xml:space="preserve">……治った。でも、心は</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.standard.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.standard.quiet[1]</t>
+          <t xml:space="preserve">autumnWarChampion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7983,14 +7983,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふたりで積み上げた結果です。うれしいです。</t>
+          <t xml:space="preserve">みんなで勝ち取った勝利です。</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">bestMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8015,14 +8015,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドーム、ですか</t>
+          <t xml:space="preserve">……あの試合のことは、ずっと体が覚えてる</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8047,14 +8047,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やります</t>
+          <t xml:space="preserve">……この重さを、背負い続ける</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.quiet[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[3]</t>
+          <t xml:space="preserve">hallOfFame.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8079,14 +8079,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（無言で頷く）</t>
+          <t xml:space="preserve">……ありがとう。この場所が、私の全部だった</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">mediaAward.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8111,14 +8111,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員でした</t>
+          <t xml:space="preserve">…ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8128,12 +8128,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">mvp.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8143,14 +8143,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう、ございます</t>
+          <t xml:space="preserve">……一試合、一試合。それだけをやった</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.quiet[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[3]</t>
+          <t xml:space="preserve">rookie.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8175,14 +8175,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（深く頭を下げる）</t>
+          <t xml:space="preserve">……まだ何も成し遂げていない。これから</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8192,29 +8192,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.quiet[1]</t>
+          <t xml:space="preserve">springTagChampion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……少し、手応えがある</t>
+          <t xml:space="preserve">ふたりで積み上げた結果です。うれしいです。</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8224,29 +8224,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いい人たちだと、思います</t>
+          <t xml:space="preserve">…ドーム、ですか</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8256,29 +8256,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……少し、休みます</t>
+          <t xml:space="preserve">…やります</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8288,29 +8288,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……応援、ありがとうございます</t>
+          <t xml:space="preserve">……（無言で頷く）</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8320,29 +8320,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（何も言わず、目を逸らす）</t>
+          <t xml:space="preserve">…満員でした</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.standard.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8352,29 +8352,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この場所に感謝している</t>
+          <t xml:space="preserve">…ありがとう、ございます</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8384,29 +8384,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（何も言わず、封筒を見つめている）</t>
+          <t xml:space="preserve">……（深く頭を下げる）</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8416,29 +8416,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.quiet[1]</t>
+          <t xml:space="preserve">N1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとうございます</t>
+          <t xml:space="preserve">……少し、手応えがある</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8448,29 +8448,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.quiet[1]</t>
+          <t xml:space="preserve">N2.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……頑張ります</t>
+          <t xml:space="preserve">……いい人たちだと、思います</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8480,29 +8480,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.standard.quiet[1]</t>
+          <t xml:space="preserve">N3.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ずっと、見てくれてたんですね</t>
+          <t xml:space="preserve">……少し、休みます</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8512,29 +8512,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.quiet[1]</t>
+          <t xml:space="preserve">N4.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ありがとう、ございます</t>
+          <t xml:space="preserve">……応援、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8544,29 +8544,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.quiet[1]</t>
+          <t xml:space="preserve">N5_low.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう、ですか</t>
+          <t xml:space="preserve">………（何も言わず、目を逸らす）</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.quiet[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8576,29 +8576,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.quiet[2]</t>
+          <t xml:space="preserve">breakthrough.voice.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……はい。わかりました</t>
+          <t xml:space="preserve">…この場所に感謝している</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.standard.quiet[1]</t>
+          <t xml:space="preserve">bonus_insult.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8623,14 +8623,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…が、頑張ります</t>
+          <t xml:space="preserve">…………（何も言わず、封筒を見つめている）</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.quiet[1]</t>
+          <t xml:space="preserve">bonus.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8655,14 +8655,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……楽しかったです（小さく微笑んでいる）</t>
+          <t xml:space="preserve">……ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.standard.quiet[1]</t>
+          <t xml:space="preserve">camp.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8687,14 +8687,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し、休みます。ありがとうございます</t>
+          <t xml:space="preserve">……頑張ります</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.standard.quiet[1]</t>
+          <t xml:space="preserve">encourage_high_trust.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8719,14 +8719,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。早く、戻ります</t>
+          <t xml:space="preserve">……ずっと、見てくれてたんですね</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.standard.quiet[1]</t>
+          <t xml:space="preserve">encourage.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全力で、学びます</t>
+          <t xml:space="preserve">………ありがとう、ございます</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.standard.quiet[1]</t>
+          <t xml:space="preserve">faction_decree.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8783,14 +8783,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出演のお話、ですか…頑張ります</t>
+          <t xml:space="preserve">……そう、ですか</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.standard.quiet[1]</t>
+          <t xml:space="preserve">faction_decree.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8815,14 +8815,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………他から、話が（小さな声で）</t>
+          <t xml:space="preserve">……はい。わかりました</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.quiet[1]</t>
+          <t xml:space="preserve">media.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8847,14 +8847,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（黙って道場を出ていこうとしている）</t>
+          <t xml:space="preserve">…が、頑張ります</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.quiet[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.quiet[2]</t>
+          <t xml:space="preserve">party.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8879,14 +8879,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません…今日は……</t>
+          <t xml:space="preserve">……楽しかったです（小さく微笑んでいる）</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.standard.quiet[1]</t>
+          <t xml:space="preserve">refresh_leave.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8911,14 +8911,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（黙っているが、その沈黙がかえって周囲を不安にさせている）</t>
+          <t xml:space="preserve">…少し、休みます。ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8928,12 +8928,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.standard.quiet[1]</t>
+          <t xml:space="preserve">special_treatment.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8943,14 +8943,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「…」とだけ投稿。ファンの間で憶測が広がっている）</t>
+          <t xml:space="preserve">…ありがとうございます。早く、戻ります</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.standard.quiet[1]</t>
+          <t xml:space="preserve">trainer.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8975,14 +8975,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……挑戦させてください</t>
+          <t xml:space="preserve">……全力で、学びます</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.standard.quiet[1]</t>
+          <t xml:space="preserve">E1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9007,14 +9007,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの人と、戦わせてください</t>
+          <t xml:space="preserve">…出演のお話、ですか…頑張ります</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.standard.quiet[1]</t>
+          <t xml:space="preserve">E6.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9039,14 +9039,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……少し、休ませてください</t>
+          <t xml:space="preserve">………他から、話が（小さな声で）</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.standard.quiet[1]</t>
+          <t xml:space="preserve">S_boycott.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9071,14 +9071,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（険しい目でこちらを見つめている）</t>
+          <t xml:space="preserve">…………（黙って道場を出ていこうとしている）</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.standard.quiet[1]</t>
+          <t xml:space="preserve">S_boycott.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9103,14 +9103,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（小さくため息をつき、視線を逸らす）</t>
+          <t xml:space="preserve">……すみません…今日は……</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.standard.quiet[1]</t>
+          <t xml:space="preserve">S_grumble.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9135,14 +9135,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……特訓、させてください</t>
+          <t xml:space="preserve">（黙っているが、その沈黙がかえって周囲を不安にさせている）</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.standard.quiet[1]</t>
+          <t xml:space="preserve">S_sns.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9167,14 +9167,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……後輩に、伝えたいことがあるんです</t>
+          <t xml:space="preserve">（SNSに「…」とだけ投稿。ファンの間で憶測が広がっている）</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.standard.quiet[1]</t>
+          <t xml:space="preserve">S1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9199,14 +9199,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出る。頑張る</t>
+          <t xml:space="preserve">……挑戦させてください</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.standard.quiet[1]</t>
+          <t xml:space="preserve">S2.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9231,14 +9231,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……私で、いいんですか。……やります</t>
+          <t xml:space="preserve">……あの人と、戦わせてください</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.standard.quiet[1]</t>
+          <t xml:space="preserve">S3.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9263,14 +9263,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません</t>
+          <t xml:space="preserve">……少し、休ませてください</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.standard.quiet[1]</t>
+          <t xml:space="preserve">S4_direct.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9295,14 +9295,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………あの人とは、もう…</t>
+          <t xml:space="preserve">………（険しい目でこちらを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.standard.quiet[1]</t>
+          <t xml:space="preserve">S4_silent.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9327,14 +9327,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに俯いている）</t>
+          <t xml:space="preserve">…………（小さくため息をつき、視線を逸らす）</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.standard.quiet[1]</t>
+          <t xml:space="preserve">S5.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9359,14 +9359,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかりました。やります</t>
+          <t xml:space="preserve">……特訓、させてください</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9376,12 +9376,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.standard.quiet[1]</t>
+          <t xml:space="preserve">S6.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9391,14 +9391,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やります</t>
+          <t xml:space="preserve">……後輩に、伝えたいことがあるんです</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.standard.quiet[1]</t>
+          <t xml:space="preserve">E1.accept.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9423,14 +9423,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンの人たちと話す。ちゃんとやります</t>
+          <t xml:space="preserve">……出る。頑張る</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.standard.quiet[1]</t>
+          <t xml:space="preserve">E1.recommend.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9455,14 +9455,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…歩けばいいんですね。やります</t>
+          <t xml:space="preserve">……私で、いいんですか。……やります</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.standard.quiet[1]</t>
+          <t xml:space="preserve">B1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9487,14 +9487,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…撮るだけですよね。わかりました</t>
+          <t xml:space="preserve">……すみません</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.standard.quiet[1]</t>
+          <t xml:space="preserve">B2_fighter1.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9519,14 +9519,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…喋るんですか。少し、緊張します</t>
+          <t xml:space="preserve">………あの人とは、もう…</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.standard.quiet[1]</t>
+          <t xml:space="preserve">B2_fighter2.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9551,14 +9551,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…がんばります</t>
+          <t xml:space="preserve">………（静かに俯いている）</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9568,29 +9568,29 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">B4_brand.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………よろしくお願いします</t>
+          <t xml:space="preserve">…わかりました。やります</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9600,29 +9600,29 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">B4_cm.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくお願いします</t>
+          <t xml:space="preserve">…やります</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9632,29 +9632,29 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">B4_fan.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（深々と一礼）</t>
+          <t xml:space="preserve">…ファンの人たちと話す。ちゃんとやります</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.quiet[3]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9664,29 +9664,29 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[3]</t>
+          <t xml:space="preserve">B4_fashion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全力でやります</t>
+          <t xml:space="preserve">…歩けばいいんですね。やります</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9696,29 +9696,29 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">B4_gravure.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくお願いします</t>
+          <t xml:space="preserve">…撮るだけですよね。わかりました</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9728,29 +9728,29 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">B4_variety.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくお願いします</t>
+          <t xml:space="preserve">…喋るんですか。少し、緊張します</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9760,29 +9760,29 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">B4.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…（静かに頭を下げる）</t>
+          <t xml:space="preserve">…がんばります</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.quiet[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9792,12 +9792,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[3]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9807,14 +9807,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめん</t>
+          <t xml:space="preserve">………よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9824,12 +9824,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9839,14 +9839,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（終わったはずの相手を、じっと見ている）</t>
+          <t xml:space="preserve">…よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9871,14 +9871,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（あの日の敗北の瞬間が、まだ耳から抜けない）</t>
+          <t xml:space="preserve">………（深々と一礼）</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9903,14 +9903,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………よろしくお願いします</t>
+          <t xml:space="preserve">……全力でやります</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9920,12 +9920,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9942,7 +9942,7 @@
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.quiet[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.quiet[2]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9967,14 +9967,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（深々と一礼）</t>
+          <t xml:space="preserve">…よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.quiet[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.quiet[3]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -9999,14 +9999,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全力でやります</t>
+          <t xml:space="preserve">…（静かに頭を下げる）</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10031,14 +10031,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう一度、リングに立てるんですね</t>
+          <t xml:space="preserve">…ごめん</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.quiet[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10063,14 +10063,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…声がかかって、よかったです</t>
+          <t xml:space="preserve">………（終わったはずの相手を、じっと見ている）</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.standard.quiet[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10095,14 +10095,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくお願いします</t>
+          <t xml:space="preserve">………（あの日の敗北の瞬間が、まだ耳から抜けない）</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.standard.quiet[1]</t>
+          <t xml:space="preserve">draftInterest.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10127,14 +10127,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくお願いします</t>
+          <t xml:space="preserve">………よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.standard.quiet[1]</t>
+          <t xml:space="preserve">draftJoin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10159,14 +10159,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が、軽いです。…今日は、いけます</t>
+          <t xml:space="preserve">…よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.standard.quiet[1]</t>
+          <t xml:space="preserve">draftJoin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10191,14 +10191,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が、重いです。…今日は、たぶん、残りません</t>
+          <t xml:space="preserve">………（深々と一礼）</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.standard.quiet[1]</t>
+          <t xml:space="preserve">draftJoin.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10223,14 +10223,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…同じことを、しているのに。…返るものが、少ない</t>
+          <t xml:space="preserve">……全力でやります</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.quiet[2]</t>
+          <t xml:space="preserve">faGreeting.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10255,14 +10255,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…（静かに頭を下げる）</t>
+          <t xml:space="preserve">…もう一度、リングに立てるんですね</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.quiet[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.quiet[3]</t>
+          <t xml:space="preserve">faGreeting.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10287,14 +10287,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめん</t>
+          <t xml:space="preserve">…声がかかって、よかったです</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.quiet[1]</t>
+          <t xml:space="preserve">faSigning.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10319,14 +10319,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（深く一礼）</t>
+          <t xml:space="preserve">…よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.quiet[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.quiet[3]</t>
+          <t xml:space="preserve">faWelcome.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10351,14 +10351,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お世話になりました</t>
+          <t xml:space="preserve">…よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.standard.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10383,14 +10383,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間ですが、よろしくお願いします</t>
+          <t xml:space="preserve">…体が、軽いです。…今日は、いけます</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10415,14 +10415,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていてくれた人が、いたんですね</t>
+          <t xml:space="preserve">…体が、重いです。…今日は、たぶん、残りません</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.quiet[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.quiet[2]</t>
+          <t xml:space="preserve">heatSelf.warm.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10447,14 +10447,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…がんばります。…それだけ、です</t>
+          <t xml:space="preserve">…同じことを、しているのに。…返るものが、少ない</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.standard.quiet[1]</t>
+          <t xml:space="preserve">injury.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10479,14 +10479,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（唇を噛んでいる）</t>
+          <t xml:space="preserve">…（静かに頭を下げる）</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.standard.quiet[1]</t>
+          <t xml:space="preserve">injury.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10511,14 +10511,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">…ごめん</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.standard.quiet[1]</t>
+          <t xml:space="preserve">release.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10543,14 +10543,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今は…一人にしてください</t>
+          <t xml:space="preserve">……（深く一礼）</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.quiet[1]</t>
+          <t xml:space="preserve">release.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10575,14 +10575,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（ベルトを抱きしめている）</t>
+          <t xml:space="preserve">…お世話になりました</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10592,12 +10592,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">rentalGreeting.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10607,14 +10607,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（深く一礼）</t>
+          <t xml:space="preserve">…短い間ですが、よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.quiet[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[3]</t>
+          <t xml:space="preserve">scoutGreeting.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10639,14 +10639,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お世話になりました</t>
+          <t xml:space="preserve">…見ていてくれた人が、いたんですね</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10656,12 +10656,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">scoutGreeting.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10671,14 +10671,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…短い間ですが、よろしくお願いします</t>
+          <t xml:space="preserve">…がんばります。…それだけ、です</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10710,7 +10710,7 @@
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10720,12 +10720,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">titleDefense.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10742,7 +10742,7 @@
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">titleLoss.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10774,7 +10774,7 @@
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">titleWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10806,7 +10806,7 @@
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.standard[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10816,29 +10816,29 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.quiet.standard[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、終わりだ</t>
+          <t xml:space="preserve">……（深く一礼）</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.standard[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10848,29 +10848,29 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.standard[1]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……遠くなった</t>
+          <t xml:space="preserve">…お世話になりました</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.standard[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10880,29 +10880,29 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.standard[2]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……気づけば、隣にいない</t>
+          <t xml:space="preserve">…短い間ですが、よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10912,29 +10912,29 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.standard[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最近、隣にいると落ち着く</t>
+          <t xml:space="preserve">………（唇を噛んでいる）</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.standard[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10944,29 +10944,29 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.standard[2]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この距離が、静かで心地いい</t>
+          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10976,29 +10976,29 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.standard[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……私の光だ</t>
+          <t xml:space="preserve">……今は…一人にしてください</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.standard[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11008,29 +11008,29 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.standard[2]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そばにいてくれれば、それでいい</t>
+          <t xml:space="preserve">………（ベルトを抱きしめている）</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.standard[1]</t>
+          <t xml:space="preserve">bond_39_down.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11055,14 +11055,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、考えない</t>
+          <t xml:space="preserve">……もう、終わりだ</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.standard[2]</t>
+          <t xml:space="preserve">bond_59_down.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11087,14 +11087,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……風が止んだ。そんな感覚だ</t>
+          <t xml:space="preserve">……遠くなった</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.standard[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11119,14 +11119,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……考えてしまう。どうしても</t>
+          <t xml:space="preserve">……気づけば、隣にいない</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.standard[2]</t>
+          <t xml:space="preserve">bond_60_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11151,14 +11151,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……燃えている。自分の中の何かが</t>
+          <t xml:space="preserve">……最近、隣にいると落ち着く</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.standard[1]</t>
+          <t xml:space="preserve">bond_60_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11183,14 +11183,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認めたくないけど、意識してる</t>
+          <t xml:space="preserve">……この距離が、静かで心地いい</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.standard[2]</t>
+          <t xml:space="preserve">bond_80_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11215,14 +11215,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そのことばかり考えている</t>
+          <t xml:space="preserve">……私の光だ</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.standard[1]</t>
+          <t xml:space="preserve">bond_80_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11247,14 +11247,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この相手がいる限り、リングに立ち続ける</t>
+          <t xml:space="preserve">……そばにいてくれれば、それでいい</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.standard[2]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11279,14 +11279,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……言葉はいらない。リングの上で語り合おう</t>
+          <t xml:space="preserve">……もう、考えない</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.standard[1]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11311,14 +11311,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいたい。ずっと</t>
+          <t xml:space="preserve">……風が止んだ。そんな感覚だ</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.standard[2]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11343,14 +11343,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この場所を、守りたい</t>
+          <t xml:space="preserve">……考えてしまう。どうしても</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.standard[1]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11375,14 +11375,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（荷物をまとめ始めている）</t>
+          <t xml:space="preserve">……燃えている。自分の中の何かが</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.standard[2]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11407,14 +11407,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、何も感じない</t>
+          <t xml:space="preserve">……認めたくないけど、意識してる</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.quiet.standard[1]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11439,14 +11439,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいていいのか、分からなくなってきた</t>
+          <t xml:space="preserve">……そのことばかり考えている</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.quiet[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11471,14 +11471,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けた。でも…悪くなかった</t>
+          <t xml:space="preserve">……この相手がいる限り、リングに立ち続ける</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11488,12 +11488,12 @@
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.quiet[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11503,14 +11503,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（小さくガッツポーズをしている）</t>
+          <t xml:space="preserve">……言葉はいらない。リングの上で語り合おう</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.quiet[2]</t>
+          <t xml:space="preserve">trust_above_75.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11535,14 +11535,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いい試合だった。全てが噛み合った</t>
+          <t xml:space="preserve">……ここにいたい。ずっと</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.quiet[2]</t>
+          <t xml:space="preserve">trust_above_75.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11567,14 +11567,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（無言で拳を握りしめている）</t>
+          <t xml:space="preserve">……この場所を、守りたい</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11584,12 +11584,12 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.quiet[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11599,14 +11599,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">……（荷物をまとめ始めている）</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.standard[2]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.quiet[2]</t>
+          <t xml:space="preserve">trust_below_20.quiet.standard[2]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11631,14 +11631,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くない</t>
+          <t xml:space="preserve">……もう、何も感じない</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.standard[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11648,12 +11648,12 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.quiet[1]</t>
+          <t xml:space="preserve">trust_below_35.quiet.standard[1]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11663,14 +11663,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（黙々とスクワットを続けている）</t>
+          <t xml:space="preserve">……ここにいていいのか、分からなくなってきた</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11695,14 +11695,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（汗が床に落ちる音だけが響く）</t>
+          <t xml:space="preserve">……負けた。でも…悪くなかった</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11727,14 +11727,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（不安そうに窓の外を見ている）</t>
+          <t xml:space="preserve">……（小さくガッツポーズをしている）</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11759,14 +11759,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいてもいいんだな</t>
+          <t xml:space="preserve">……いい試合だった。全てが噛み合った</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-01.loss.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11791,14 +11791,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（そっと隣を見て、少し微笑んでいる）</t>
+          <t xml:space="preserve">……（無言で拳を握りしめている）</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-01.win.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11823,14 +11823,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（試合映像を食い入るように見ている）</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-01.win.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11855,14 +11855,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（リングを見つめている）</t>
+          <t xml:space="preserve">……悪くない</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-02.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -11887,14 +11887,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出番がない。ただそれだけが、重い</t>
+          <t xml:space="preserve">……（黙々とスクワットを続けている）</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-02.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -11919,14 +11919,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が、動かない</t>
+          <t xml:space="preserve">………（汗が床に落ちる音だけが響く）</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -11951,14 +11951,14 @@
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（無言で練習を続けている）</t>
+          <t xml:space="preserve">……（不安そうに窓の外を見ている）</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-03.up.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -11983,14 +11983,14 @@
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（壁に拳を押し当てている）</t>
+          <t xml:space="preserve">……ここにいてもいいんだな</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-04.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -12015,14 +12015,14 @@
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いい流れだ。このまま</t>
+          <t xml:space="preserve">……（そっと隣を見て、少し微笑んでいる）</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-05.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -12047,14 +12047,14 @@
       </c>
       <c r="F367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（天井を見つめている）</t>
+          <t xml:space="preserve">……（試合映像を食い入るように見ている）</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-06.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -12079,14 +12079,14 @@
       </c>
       <c r="F368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……リングが、遠い</t>
+          <t xml:space="preserve">……（リングを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-06.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -12111,14 +12111,14 @@
       </c>
       <c r="F369" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（視線は合わせない）</t>
+          <t xml:space="preserve">……出番がない。ただそれだけが、重い</t>
         </is>
       </c>
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">GL-07.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -12143,14 +12143,14 @@
       </c>
       <c r="F370" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふぅ。あの調子は続かないか</t>
+          <t xml:space="preserve">……体が、動かない</t>
         </is>
       </c>
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -12160,12 +12160,12 @@
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">GL-08.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -12175,14 +12175,14 @@
       </c>
       <c r="F371" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……元に戻った。でも…少し、違う自分になれた気がする</t>
+          <t xml:space="preserve">……（無言で練習を続けている）</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -12192,29 +12192,29 @@
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-08.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F372" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、立ってる。最後まで、いく</t>
+          <t xml:space="preserve">……（壁に拳を押し当てている）</t>
         </is>
       </c>
     </row>
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12224,29 +12224,29 @@
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-09.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F373" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……身体は重い。でも、退かない</t>
+          <t xml:space="preserve">……いい流れだ。このまま</t>
         </is>
       </c>
     </row>
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12256,29 +12256,29 @@
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-10.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F374" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……相手は誰でもいい。倒す</t>
+          <t xml:space="preserve">……（天井を見つめている）</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12288,29 +12288,29 @@
       </c>
       <c r="C375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D375" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-10.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F375" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……真っ向から。まだ、これから</t>
+          <t xml:space="preserve">……リングが、遠い</t>
         </is>
       </c>
     </row>
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12320,29 +12320,29 @@
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-11.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F376" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、落とした。まだ立ってる。……次</t>
+          <t xml:space="preserve">……（視線は合わせない）</t>
         </is>
       </c>
     </row>
     <row r="377" ht="40" customHeight="1">
       <c r="A377" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -12352,29 +12352,29 @@
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.quiet[2]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F377" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……息は上がってる。でも、退かない。……来い</t>
+          <t xml:space="preserve">……ふぅ。あの調子は続かないか</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -12384,29 +12384,29 @@
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F378" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人で、最後まで残った。それが嬉しい</t>
+          <t xml:space="preserve">……元に戻った。でも…少し、違う自分になれた気がする</t>
         </is>
       </c>
     </row>
     <row r="379" ht="40" customHeight="1">
       <c r="A379" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="C379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D379" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[2]</t>
+          <t xml:space="preserve">preFinal.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
@@ -12431,14 +12431,14 @@
       </c>
       <c r="F379" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人じゃなかった。だから、勝てた</t>
+          <t xml:space="preserve">……まだ、立ってる。最後まで、いく</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12448,12 +12448,12 @@
       </c>
       <c r="C380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D380" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[3]</t>
+          <t xml:space="preserve">preFinal.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
@@ -12463,14 +12463,14 @@
       </c>
       <c r="F380" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……仲間がいてくれた。それだけで十分</t>
+          <t xml:space="preserve">……身体は重い。でも、退かない</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12480,12 +12480,12 @@
       </c>
       <c r="C381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D381" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.quiet[1]</t>
+          <t xml:space="preserve">preMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E381" t="inlineStr" s="2">
@@ -12495,14 +12495,14 @@
       </c>
       <c r="F381" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった。次は、最後まで倒す</t>
+          <t xml:space="preserve">……相手は誰でもいい。倒す</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12512,12 +12512,12 @@
       </c>
       <c r="C382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.quiet[2]</t>
+          <t xml:space="preserve">preMatch.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12527,14 +12527,14 @@
       </c>
       <c r="F382" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……MVPでも、負けは負け。忘れない</t>
+          <t xml:space="preserve">……真っ向から。まだ、これから</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12544,12 +12544,12 @@
       </c>
       <c r="C383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.quiet[3]</t>
+          <t xml:space="preserve">survivor.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12559,14 +12559,14 @@
       </c>
       <c r="F383" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ終わってない。次がある</t>
+          <t xml:space="preserve">……一人、落とした。まだ立ってる。……次</t>
         </is>
       </c>
     </row>
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="C384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.quiet[1]</t>
+          <t xml:space="preserve">survivor.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12591,14 +12591,14 @@
       </c>
       <c r="F384" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ立ってる。だから、私の勝ち</t>
+          <t xml:space="preserve">……息は上がってる。でも、退かない。……来い</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="D385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.quiet[2]</t>
+          <t xml:space="preserve">champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
@@ -12623,14 +12623,14 @@
       </c>
       <c r="F385" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、また一人。気がついたら、最後だった</t>
+          <t xml:space="preserve">……三人で、最後まで残った。それが嬉しい</t>
         </is>
       </c>
     </row>
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="D386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.quiet[3]</t>
+          <t xml:space="preserve">champion.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
@@ -12655,14 +12655,14 @@
       </c>
       <c r="F386" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……声は出ない。でも、足はまだ動いてる</t>
+          <t xml:space="preserve">……一人じゃなかった。だから、勝てた</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12672,12 +12672,12 @@
       </c>
       <c r="C387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D387" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[1]</t>
+          <t xml:space="preserve">champion.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E387" t="inlineStr" s="2">
@@ -12687,14 +12687,14 @@
       </c>
       <c r="F387" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">……仲間がいてくれた。それだけで十分</t>
         </is>
       </c>
     </row>
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12704,12 +12704,12 @@
       </c>
       <c r="C388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D388" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[2]</t>
+          <t xml:space="preserve">defiant.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12719,14 +12719,14 @@
       </c>
       <c r="F388" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………………ありがとう</t>
+          <t xml:space="preserve">……足りなかった。次は、最後まで倒す</t>
         </is>
       </c>
     </row>
     <row r="389" ht="40" customHeight="1">
       <c r="A389" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="C389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D389" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.quiet[1]</t>
+          <t xml:space="preserve">defiant.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
@@ -12751,14 +12751,14 @@
       </c>
       <c r="F389" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………………（悔しそうに拳を握る）</t>
+          <t xml:space="preserve">……MVPでも、負けは負け。忘れない</t>
         </is>
       </c>
     </row>
     <row r="390" ht="40" customHeight="1">
       <c r="A390" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="C390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D390" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.quiet[2]</t>
+          <t xml:space="preserve">defiant.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E390" t="inlineStr" s="2">
@@ -12783,14 +12783,14 @@
       </c>
       <c r="F390" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、負けない</t>
+          <t xml:space="preserve">……まだ終わってない。次がある</t>
         </is>
       </c>
     </row>
     <row r="391" ht="40" customHeight="1">
       <c r="A391" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="C391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D391" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="2">
@@ -12815,14 +12815,14 @@
       </c>
       <c r="F391" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">……まだ立ってる。だから、私の勝ち</t>
         </is>
       </c>
     </row>
     <row r="392" ht="40" customHeight="1">
       <c r="A392" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -12832,12 +12832,12 @@
       </c>
       <c r="C392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D392" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.quiet[2]</t>
+          <t xml:space="preserve">gauntlet.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E392" t="inlineStr" s="2">
@@ -12847,14 +12847,14 @@
       </c>
       <c r="F392" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">……一人、また一人。気がついたら、最後だった</t>
         </is>
       </c>
     </row>
     <row r="393" ht="40" customHeight="1">
       <c r="A393" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="C393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D393" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E393" t="inlineStr" s="2">
@@ -12879,14 +12879,14 @@
       </c>
       <c r="F393" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……良い経験だった</t>
+          <t xml:space="preserve">……声は出ない。でも、足はまだ動いてる</t>
         </is>
       </c>
     </row>
     <row r="394" ht="40" customHeight="1">
       <c r="A394" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="D394" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.quiet[2]</t>
+          <t xml:space="preserve">champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="2">
@@ -12911,14 +12911,14 @@
       </c>
       <c r="F394" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………………（満足げに頷く）</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="395" ht="40" customHeight="1">
       <c r="A395" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="D395" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.quiet[1]</t>
+          <t xml:space="preserve">champion.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -12943,14 +12943,14 @@
       </c>
       <c r="F395" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後の一試合</t>
+          <t xml:space="preserve">………………ありがとう</t>
         </is>
       </c>
     </row>
     <row r="396" ht="40" customHeight="1">
       <c r="A396" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="D396" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.quiet[2]</t>
+          <t xml:space="preserve">postLose.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="2">
@@ -12975,14 +12975,14 @@
       </c>
       <c r="F396" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全部、出す</t>
+          <t xml:space="preserve">………………（悔しそうに拳を握る）</t>
         </is>
       </c>
     </row>
     <row r="397" ht="40" customHeight="1">
       <c r="A397" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="D397" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">postLose.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E397" t="inlineStr" s="2">
@@ -13007,14 +13007,14 @@
       </c>
       <c r="F397" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やる</t>
+          <t xml:space="preserve">……次は、負けない</t>
         </is>
       </c>
     </row>
     <row r="398" ht="40" customHeight="1">
       <c r="A398" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="D398" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.quiet[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="2">
@@ -13039,14 +13039,14 @@
       </c>
       <c r="F398" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……わかった</t>
+          <t xml:space="preserve">……次</t>
         </is>
       </c>
     </row>
     <row r="399" ht="40" customHeight="1">
       <c r="A399" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="D399" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.quiet[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -13071,14 +13071,14 @@
       </c>
       <c r="F399" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出る</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="400" ht="40" customHeight="1">
       <c r="A400" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -13088,12 +13088,12 @@
       </c>
       <c r="C400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D400" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">postWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="2">
@@ -13103,14 +13103,14 @@
       </c>
       <c r="F400" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに構えている）</t>
+          <t xml:space="preserve">……良い経験だった</t>
         </is>
       </c>
     </row>
     <row r="401" ht="40" customHeight="1">
       <c r="A401" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -13120,12 +13120,12 @@
       </c>
       <c r="C401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D401" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">postWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -13135,14 +13135,14 @@
       </c>
       <c r="F401" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（リングの上で静かに涙を流す）</t>
+          <t xml:space="preserve">………………（満足げに頷く）</t>
         </is>
       </c>
     </row>
     <row r="402" ht="40" customHeight="1">
       <c r="A402" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -13152,12 +13152,12 @@
       </c>
       <c r="C402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D402" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">preFinal.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E402" t="inlineStr" s="2">
@@ -13167,14 +13167,14 @@
       </c>
       <c r="F402" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ありがとう、ございます……（声が震えている）</t>
+          <t xml:space="preserve">……最後の一試合</t>
         </is>
       </c>
     </row>
     <row r="403" ht="40" customHeight="1">
       <c r="A403" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -13184,12 +13184,12 @@
       </c>
       <c r="C403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D403" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">preFinal.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E403" t="inlineStr" s="2">
@@ -13199,14 +13199,14 @@
       </c>
       <c r="F403" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……対抗戦を申し込む</t>
+          <t xml:space="preserve">……全部、出す</t>
         </is>
       </c>
     </row>
     <row r="404" ht="40" customHeight="1">
       <c r="A404" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -13216,12 +13216,12 @@
       </c>
       <c r="C404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D404" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">preMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E404" t="inlineStr" s="2">
@@ -13231,14 +13231,14 @@
       </c>
       <c r="F404" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戦え</t>
+          <t xml:space="preserve">……やる</t>
         </is>
       </c>
     </row>
     <row r="405" ht="40" customHeight="1">
       <c r="A405" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
@@ -13248,12 +13248,12 @@
       </c>
       <c r="C405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D405" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">summon.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E405" t="inlineStr" s="2">
@@ -13263,14 +13263,14 @@
       </c>
       <c r="F405" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか</t>
+          <t xml:space="preserve">……わかった</t>
         </is>
       </c>
     </row>
     <row r="406" ht="40" customHeight="1">
       <c r="A406" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
@@ -13280,12 +13280,12 @@
       </c>
       <c r="C406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D406" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">summon.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13295,14 +13295,14 @@
       </c>
       <c r="F406" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次はない</t>
+          <t xml:space="preserve">……出る</t>
         </is>
       </c>
     </row>
     <row r="407" ht="40" customHeight="1">
       <c r="A407" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.quiet[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
@@ -13312,12 +13312,12 @@
       </c>
       <c r="C407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D407" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E407" t="inlineStr" s="2">
@@ -13327,14 +13327,14 @@
       </c>
       <c r="F407" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悔しい</t>
+          <t xml:space="preserve">……（静かに構えている）</t>
         </is>
       </c>
     </row>
     <row r="408" ht="40" customHeight="1">
       <c r="A408" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.quiet[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="C408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D408" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.quiet[2]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
@@ -13359,14 +13359,14 @@
       </c>
       <c r="F408" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は負けない</t>
+          <t xml:space="preserve">………（リングの上で静かに涙を流す）</t>
         </is>
       </c>
     </row>
     <row r="409" ht="40" customHeight="1">
       <c r="A409" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.quiet[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="C409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D409" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E409" t="inlineStr" s="2">
@@ -13391,14 +13391,14 @@
       </c>
       <c r="F409" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">………ありがとう、ございます……（声が震えている）</t>
         </is>
       </c>
     </row>
     <row r="410" ht="40" customHeight="1">
       <c r="A410" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="C410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D410" t="inlineStr" s="12">
@@ -13423,14 +13423,14 @@
       </c>
       <c r="F410" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。団体の力を、証明できた</t>
+          <t xml:space="preserve">……対抗戦を申し込む</t>
         </is>
       </c>
     </row>
     <row r="411" ht="40" customHeight="1">
       <c r="A411" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="C411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D411" t="inlineStr" s="12">
@@ -13455,14 +13455,14 @@
       </c>
       <c r="F411" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これがうちの実力</t>
+          <t xml:space="preserve">……戦え</t>
         </is>
       </c>
     </row>
     <row r="412" ht="40" customHeight="1">
       <c r="A412" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -13472,12 +13472,12 @@
       </c>
       <c r="C412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D412" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[3]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13487,14 +13487,14 @@
       </c>
       <c r="F412" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……みんなの分も、背負って戦った</t>
+          <t xml:space="preserve">……そうか</t>
         </is>
       </c>
     </row>
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13504,29 +13504,29 @@
       </c>
       <c r="C413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F413" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ありがとうございました（静かに涙を流している）</t>
+          <t xml:space="preserve">……次はない</t>
         </is>
       </c>
     </row>
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13536,29 +13536,29 @@
       </c>
       <c r="C414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D414" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">result_lose.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F414" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう一度、リングに立てるんですね</t>
+          <t xml:space="preserve">……悔しい</t>
         </is>
       </c>
     </row>
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
@@ -13568,29 +13568,29 @@
       </c>
       <c r="C415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D415" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">result_lose.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F415" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…声がかかって、よかったです</t>
+          <t xml:space="preserve">……次は負けない</t>
         </is>
       </c>
     </row>
     <row r="416" ht="40" customHeight="1">
       <c r="A416" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
@@ -13600,59 +13600,283 @@
       </c>
       <c r="C416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D416" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">result_win.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F416" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていてくれた人が、いたんですね</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="417" ht="40" customHeight="1">
       <c r="A417" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。団体の力を、証明できた</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="40" customHeight="1">
+      <c r="A418" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……これがうちの実力</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="40" customHeight="1">
+      <c r="A419" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[3]</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[3]</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……みんなの分も、背負って戦った</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="40" customHeight="1">
+      <c r="A420" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………ありがとうございました（静かに涙を流している）</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="40" customHeight="1">
+      <c r="A421" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…もう一度、リングに立てるんですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" ht="40" customHeight="1">
+      <c r="A422" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…声がかかって、よかったです</t>
+        </is>
+      </c>
+    </row>
+    <row r="423" ht="40" customHeight="1">
+      <c r="A423" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…見ていてくれた人が、いたんですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="40" customHeight="1">
+      <c r="A424" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.quiet[2]</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr" s="2">
+      <c r="B424" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr" s="12">
+      <c r="D424" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr" s="2">
+      <c r="E424" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr" s="3">
+      <c r="F424" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…がんばります。…それだけ、です</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H417"/>
+  <autoFilter ref="A1:H424"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×寡黙.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H417"/>
+  <dimension ref="A1:H419"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -11638,7 +11638,7 @@
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11663,14 +11663,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（黙々とスクワットを続けている）</t>
+          <t xml:space="preserve">……（道具に八つ当たりしている）</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11695,14 +11695,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（汗が床に落ちる音だけが響く）</t>
+          <t xml:space="preserve">……（黙々とやっているが、目が怖い）</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-02.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11727,14 +11727,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（不安そうに窓の外を見ている）</t>
+          <t xml:space="preserve">……（黙々とスクワットを続けている）</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-02.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11759,14 +11759,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここにいてもいいんだな</t>
+          <t xml:space="preserve">………（汗が床に落ちる音だけが響く）</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11791,14 +11791,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（そっと隣を見て、少し微笑んでいる）</t>
+          <t xml:space="preserve">……（不安そうに窓の外を見ている）</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11823,14 +11823,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（試合映像を食い入るように見ている）</t>
+          <t xml:space="preserve">……ここにいてもいいんだな</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-04.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11855,14 +11855,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（リングを見つめている）</t>
+          <t xml:space="preserve">……（そっと隣を見て、少し微笑んでいる）</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-05.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -11887,14 +11887,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出番がない。ただそれだけが、重い</t>
+          <t xml:space="preserve">……（試合映像を食い入るように見ている）</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-06.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -11919,14 +11919,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が、動かない</t>
+          <t xml:space="preserve">……（リングを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-06.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -11951,14 +11951,14 @@
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（無言で練習を続けている）</t>
+          <t xml:space="preserve">……出番がない。ただそれだけが、重い</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-07.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -11983,14 +11983,14 @@
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（壁に拳を押し当てている）</t>
+          <t xml:space="preserve">……体が、動かない</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-08.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -12015,14 +12015,14 @@
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いい流れだ。このまま</t>
+          <t xml:space="preserve">……（無言で練習を続けている）</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-08.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -12047,14 +12047,14 @@
       </c>
       <c r="F367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（天井を見つめている）</t>
+          <t xml:space="preserve">……（壁に拳を押し当てている）</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.quiet[2]</t>
+          <t xml:space="preserve">GL-09.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -12079,14 +12079,14 @@
       </c>
       <c r="F368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……リングが、遠い</t>
+          <t xml:space="preserve">……いい流れだ。このまま</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.standard.quiet[1]</t>
+          <t xml:space="preserve">GL-10.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -12111,14 +12111,14 @@
       </c>
       <c r="F369" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（視線は合わせない）</t>
+          <t xml:space="preserve">……（天井を見つめている）</t>
         </is>
       </c>
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">GL-10.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -12143,14 +12143,14 @@
       </c>
       <c r="F370" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふぅ。あの調子は続かないか</t>
+          <t xml:space="preserve">……リングが、遠い</t>
         </is>
       </c>
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -12160,12 +12160,12 @@
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">GL-11.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -12175,14 +12175,14 @@
       </c>
       <c r="F371" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……元に戻った。でも…少し、違う自分になれた気がする</t>
+          <t xml:space="preserve">……（視線は合わせない）</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -12192,29 +12192,29 @@
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F372" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ、立ってる。最後まで、いく</t>
+          <t xml:space="preserve">……ふぅ。あの調子は続かないか</t>
         </is>
       </c>
     </row>
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12224,29 +12224,29 @@
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.quiet[2]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F373" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……身体は重い。でも、退かない</t>
+          <t xml:space="preserve">……元に戻った。でも…少し、違う自分になれた気がする</t>
         </is>
       </c>
     </row>
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="D374" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">preFinal.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
@@ -12271,14 +12271,14 @@
       </c>
       <c r="F374" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……相手は誰でもいい。倒す</t>
+          <t xml:space="preserve">……まだ、立ってる。最後まで、いく</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="D375" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.quiet[2]</t>
+          <t xml:space="preserve">preFinal.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E375" t="inlineStr" s="2">
@@ -12303,14 +12303,14 @@
       </c>
       <c r="F375" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……真っ向から。まだ、これから</t>
+          <t xml:space="preserve">……身体は重い。でも、退かない</t>
         </is>
       </c>
     </row>
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="D376" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.quiet[1]</t>
+          <t xml:space="preserve">preMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E376" t="inlineStr" s="2">
@@ -12335,14 +12335,14 @@
       </c>
       <c r="F376" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、落とした。まだ立ってる。……次</t>
+          <t xml:space="preserve">……相手は誰でもいい。倒す</t>
         </is>
       </c>
     </row>
     <row r="377" ht="40" customHeight="1">
       <c r="A377" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -12357,7 +12357,7 @@
       </c>
       <c r="D377" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.quiet[2]</t>
+          <t xml:space="preserve">preMatch.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E377" t="inlineStr" s="2">
@@ -12367,14 +12367,14 @@
       </c>
       <c r="F377" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……息は上がってる。でも、退かない。……来い</t>
+          <t xml:space="preserve">……真っ向から。まだ、これから</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -12384,12 +12384,12 @@
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[1]</t>
+          <t xml:space="preserve">survivor.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E378" t="inlineStr" s="2">
@@ -12399,14 +12399,14 @@
       </c>
       <c r="F378" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人で、最後まで残った。それが嬉しい</t>
+          <t xml:space="preserve">……一人、落とした。まだ立ってる。……次</t>
         </is>
       </c>
     </row>
     <row r="379" ht="40" customHeight="1">
       <c r="A379" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="C379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D379" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[2]</t>
+          <t xml:space="preserve">survivor.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
@@ -12431,14 +12431,14 @@
       </c>
       <c r="F379" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人じゃなかった。だから、勝てた</t>
+          <t xml:space="preserve">……息は上がってる。でも、退かない。……来い</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="D380" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[3]</t>
+          <t xml:space="preserve">champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
@@ -12463,14 +12463,14 @@
       </c>
       <c r="F380" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……仲間がいてくれた。それだけで十分</t>
+          <t xml:space="preserve">……三人で、最後まで残った。それが嬉しい</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="D381" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.quiet[1]</t>
+          <t xml:space="preserve">champion.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E381" t="inlineStr" s="2">
@@ -12495,14 +12495,14 @@
       </c>
       <c r="F381" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった。次は、最後まで倒す</t>
+          <t xml:space="preserve">……一人じゃなかった。だから、勝てた</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="D382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.quiet[2]</t>
+          <t xml:space="preserve">champion.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12527,14 +12527,14 @@
       </c>
       <c r="F382" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……MVPでも、負けは負け。忘れない</t>
+          <t xml:space="preserve">……仲間がいてくれた。それだけで十分</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="D383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.quiet[3]</t>
+          <t xml:space="preserve">defiant.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12559,14 +12559,14 @@
       </c>
       <c r="F383" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ終わってない。次がある</t>
+          <t xml:space="preserve">……足りなかった。次は、最後まで倒す</t>
         </is>
       </c>
     </row>
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="D384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.quiet[1]</t>
+          <t xml:space="preserve">defiant.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12591,14 +12591,14 @@
       </c>
       <c r="F384" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ立ってる。だから、私の勝ち</t>
+          <t xml:space="preserve">……MVPでも、負けは負け。忘れない</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="D385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.quiet[2]</t>
+          <t xml:space="preserve">defiant.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
@@ -12623,14 +12623,14 @@
       </c>
       <c r="F385" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、また一人。気がついたら、最後だった</t>
+          <t xml:space="preserve">……まだ終わってない。次がある</t>
         </is>
       </c>
     </row>
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="D386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.quiet[3]</t>
+          <t xml:space="preserve">gauntlet.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
@@ -12655,14 +12655,14 @@
       </c>
       <c r="F386" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……声は出ない。でも、足はまだ動いてる</t>
+          <t xml:space="preserve">……まだ立ってる。だから、私の勝ち</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12672,12 +12672,12 @@
       </c>
       <c r="C387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D387" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E387" t="inlineStr" s="2">
@@ -12687,14 +12687,14 @@
       </c>
       <c r="F387" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">……一人、また一人。気がついたら、最後だった</t>
         </is>
       </c>
     </row>
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12704,12 +12704,12 @@
       </c>
       <c r="C388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D388" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.quiet[2]</t>
+          <t xml:space="preserve">gauntlet.standard.quiet[3]</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12719,14 +12719,14 @@
       </c>
       <c r="F388" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………………ありがとう</t>
+          <t xml:space="preserve">……声は出ない。でも、足はまだ動いてる</t>
         </is>
       </c>
     </row>
     <row r="389" ht="40" customHeight="1">
       <c r="A389" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="D389" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.quiet[1]</t>
+          <t xml:space="preserve">champion.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
@@ -12751,14 +12751,14 @@
       </c>
       <c r="F389" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………………（悔しそうに拳を握る）</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="390" ht="40" customHeight="1">
       <c r="A390" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="D390" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.quiet[2]</t>
+          <t xml:space="preserve">champion.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E390" t="inlineStr" s="2">
@@ -12783,14 +12783,14 @@
       </c>
       <c r="F390" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、負けない</t>
+          <t xml:space="preserve">………………ありがとう</t>
         </is>
       </c>
     </row>
     <row r="391" ht="40" customHeight="1">
       <c r="A391" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="D391" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.quiet[1]</t>
+          <t xml:space="preserve">postLose.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="2">
@@ -12815,14 +12815,14 @@
       </c>
       <c r="F391" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">………………（悔しそうに拳を握る）</t>
         </is>
       </c>
     </row>
     <row r="392" ht="40" customHeight="1">
       <c r="A392" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="D392" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.quiet[2]</t>
+          <t xml:space="preserve">postLose.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E392" t="inlineStr" s="2">
@@ -12847,14 +12847,14 @@
       </c>
       <c r="F392" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">……次は、負けない</t>
         </is>
       </c>
     </row>
     <row r="393" ht="40" customHeight="1">
       <c r="A393" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="D393" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.quiet[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E393" t="inlineStr" s="2">
@@ -12879,14 +12879,14 @@
       </c>
       <c r="F393" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……良い経験だった</t>
+          <t xml:space="preserve">……次</t>
         </is>
       </c>
     </row>
     <row r="394" ht="40" customHeight="1">
       <c r="A394" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="D394" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.quiet[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="2">
@@ -12911,14 +12911,14 @@
       </c>
       <c r="F394" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………………（満足げに頷く）</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="395" ht="40" customHeight="1">
       <c r="A395" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="D395" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.quiet[1]</t>
+          <t xml:space="preserve">postWin.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -12943,14 +12943,14 @@
       </c>
       <c r="F395" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後の一試合</t>
+          <t xml:space="preserve">……良い経験だった</t>
         </is>
       </c>
     </row>
     <row r="396" ht="40" customHeight="1">
       <c r="A396" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="D396" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.quiet[2]</t>
+          <t xml:space="preserve">postWin.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="2">
@@ -12975,14 +12975,14 @@
       </c>
       <c r="F396" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……全部、出す</t>
+          <t xml:space="preserve">………………（満足げに頷く）</t>
         </is>
       </c>
     </row>
     <row r="397" ht="40" customHeight="1">
       <c r="A397" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="D397" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.quiet[1]</t>
+          <t xml:space="preserve">preFinal.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E397" t="inlineStr" s="2">
@@ -13007,14 +13007,14 @@
       </c>
       <c r="F397" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やる</t>
+          <t xml:space="preserve">……最後の一試合</t>
         </is>
       </c>
     </row>
     <row r="398" ht="40" customHeight="1">
       <c r="A398" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="D398" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.quiet[1]</t>
+          <t xml:space="preserve">preFinal.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="2">
@@ -13039,14 +13039,14 @@
       </c>
       <c r="F398" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……わかった</t>
+          <t xml:space="preserve">……全部、出す</t>
         </is>
       </c>
     </row>
     <row r="399" ht="40" customHeight="1">
       <c r="A399" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.quiet[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="D399" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.quiet[2]</t>
+          <t xml:space="preserve">preMatch.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -13071,14 +13071,14 @@
       </c>
       <c r="F399" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……出る</t>
+          <t xml:space="preserve">……やる</t>
         </is>
       </c>
     </row>
     <row r="400" ht="40" customHeight="1">
       <c r="A400" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -13088,12 +13088,12 @@
       </c>
       <c r="C400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D400" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">summon.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="2">
@@ -13103,14 +13103,14 @@
       </c>
       <c r="F400" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに構えている）</t>
+          <t xml:space="preserve">……わかった</t>
         </is>
       </c>
     </row>
     <row r="401" ht="40" customHeight="1">
       <c r="A401" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -13120,12 +13120,12 @@
       </c>
       <c r="C401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D401" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">summon.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -13135,14 +13135,14 @@
       </c>
       <c r="F401" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（リングの上で静かに涙を流す）</t>
+          <t xml:space="preserve">……出る</t>
         </is>
       </c>
     </row>
     <row r="402" ht="40" customHeight="1">
       <c r="A402" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -13152,12 +13152,12 @@
       </c>
       <c r="C402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D402" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E402" t="inlineStr" s="2">
@@ -13167,14 +13167,14 @@
       </c>
       <c r="F402" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ありがとう、ございます……（声が震えている）</t>
+          <t xml:space="preserve">……（静かに構えている）</t>
         </is>
       </c>
     </row>
     <row r="403" ht="40" customHeight="1">
       <c r="A403" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.quiet[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D403" t="inlineStr" s="12">
@@ -13199,14 +13199,14 @@
       </c>
       <c r="F403" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……対抗戦を申し込む</t>
+          <t xml:space="preserve">………（リングの上で静かに涙を流す）</t>
         </is>
       </c>
     </row>
     <row r="404" ht="40" customHeight="1">
       <c r="A404" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.quiet[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="C404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D404" t="inlineStr" s="12">
@@ -13231,14 +13231,14 @@
       </c>
       <c r="F404" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戦え</t>
+          <t xml:space="preserve">………ありがとう、ございます……（声が震えている）</t>
         </is>
       </c>
     </row>
     <row r="405" ht="40" customHeight="1">
       <c r="A405" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="C405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D405" t="inlineStr" s="12">
@@ -13263,14 +13263,14 @@
       </c>
       <c r="F405" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか</t>
+          <t xml:space="preserve">……対抗戦を申し込む</t>
         </is>
       </c>
     </row>
     <row r="406" ht="40" customHeight="1">
       <c r="A406" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.quiet[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="C406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D406" t="inlineStr" s="12">
@@ -13295,14 +13295,14 @@
       </c>
       <c r="F406" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次はない</t>
+          <t xml:space="preserve">……戦え</t>
         </is>
       </c>
     </row>
     <row r="407" ht="40" customHeight="1">
       <c r="A407" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
@@ -13312,12 +13312,12 @@
       </c>
       <c r="C407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D407" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E407" t="inlineStr" s="2">
@@ -13327,14 +13327,14 @@
       </c>
       <c r="F407" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悔しい</t>
+          <t xml:space="preserve">……そうか</t>
         </is>
       </c>
     </row>
     <row r="408" ht="40" customHeight="1">
       <c r="A408" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.quiet[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="C408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D408" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.quiet[2]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
@@ -13359,14 +13359,14 @@
       </c>
       <c r="F408" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は負けない</t>
+          <t xml:space="preserve">……次はない</t>
         </is>
       </c>
     </row>
     <row r="409" ht="40" customHeight="1">
       <c r="A409" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="D409" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.quiet[1]</t>
+          <t xml:space="preserve">result_lose.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E409" t="inlineStr" s="2">
@@ -13391,14 +13391,14 @@
       </c>
       <c r="F409" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った</t>
+          <t xml:space="preserve">……悔しい</t>
         </is>
       </c>
     </row>
     <row r="410" ht="40" customHeight="1">
       <c r="A410" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
@@ -13408,12 +13408,12 @@
       </c>
       <c r="C410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D410" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">result_lose.standard.quiet[2]</t>
         </is>
       </c>
       <c r="E410" t="inlineStr" s="2">
@@ -13423,14 +13423,14 @@
       </c>
       <c r="F410" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。団体の力を、証明できた</t>
+          <t xml:space="preserve">……次は負けない</t>
         </is>
       </c>
     </row>
     <row r="411" ht="40" customHeight="1">
       <c r="A411" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -13440,12 +13440,12 @@
       </c>
       <c r="C411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D411" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">result_win.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
@@ -13455,14 +13455,14 @@
       </c>
       <c r="F411" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これがうちの実力</t>
+          <t xml:space="preserve">……勝った</t>
         </is>
       </c>
     </row>
     <row r="412" ht="40" customHeight="1">
       <c r="A412" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -13477,7 +13477,7 @@
       </c>
       <c r="D412" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[3]</t>
+          <t xml:space="preserve">standard.quiet[1]</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13487,14 +13487,14 @@
       </c>
       <c r="F412" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……みんなの分も、背負って戦った</t>
+          <t xml:space="preserve">……勝った。団体の力を、証明できた</t>
         </is>
       </c>
     </row>
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[2]</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13504,29 +13504,29 @@
       </c>
       <c r="C413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F413" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………ありがとうございました（静かに涙を流している）</t>
+          <t xml:space="preserve">……これがうちの実力</t>
         </is>
       </c>
     </row>
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.quiet[3]</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13536,29 +13536,29 @@
       </c>
       <c r="C414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D414" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[1]</t>
+          <t xml:space="preserve">standard.quiet[3]</t>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F414" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう一度、リングに立てるんですね</t>
+          <t xml:space="preserve">……みんなの分も、背負って戦った</t>
         </is>
       </c>
     </row>
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.quiet[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
@@ -13568,29 +13568,29 @@
       </c>
       <c r="C415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D415" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.quiet[2]</t>
+          <t xml:space="preserve">fighter.standard.quiet[1]</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F415" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…声がかかって、よかったです</t>
+          <t xml:space="preserve">………ありがとうございました（静かに涙を流している）</t>
         </is>
       </c>
     </row>
     <row r="416" ht="40" customHeight="1">
       <c r="A416" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.quiet[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.quiet[1]</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
@@ -13600,7 +13600,7 @@
       </c>
       <c r="C416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D416" t="inlineStr" s="12">
@@ -13615,44 +13615,108 @@
       </c>
       <c r="F416" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていてくれた人が、いたんですね</t>
+          <t xml:space="preserve">…もう一度、リングに立てるんですね</t>
         </is>
       </c>
     </row>
     <row r="417" ht="40" customHeight="1">
       <c r="A417" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…声がかかって、よかったです</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="40" customHeight="1">
+      <c r="A418" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…見ていてくれた人が、いたんですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="40" customHeight="1">
+      <c r="A419" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.quiet[2]</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr" s="2">
+      <c r="B419" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr" s="12">
+      <c r="D419" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.quiet[2]</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr" s="2">
+      <c r="E419" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr" s="3">
+      <c r="F419" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…がんばります。…それだけ、です</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H417"/>
+  <autoFilter ref="A1:H419"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×寡黙.xlsx
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。あの人と、やらせてください。</t>
+          <t xml:space="preserve">社長。三人で、行かせてください。</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……お願いがあります。あの人です。</t>
+          <t xml:space="preserve">……お願いがあります。三人での、遠征です。</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一つだけ。あの人と、組んでください。</t>
+          <t xml:space="preserve">一つだけ。あちらへ三人で、組んでください。</t>
         </is>
       </c>
     </row>
